--- a/eduservices/DRILL1_EXCEL.xlsx
+++ b/eduservices/DRILL1_EXCEL.xlsx
@@ -166,7 +166,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -188,13 +188,13 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="6" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="6" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="6" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="6" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="6" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -224,6 +224,9 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
@@ -781,27 +784,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S59"/>
+  <dimension ref="A1:X59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.5" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="3" customWidth="1" min="13" max="13"/>
-    <col width="13" customWidth="1" min="14" max="14"/>
-    <col width="13" customWidth="1" min="15" max="15"/>
-    <col width="13" customWidth="1" min="16" max="16"/>
-    <col width="13" customWidth="1" min="17" max="17"/>
-    <col width="13" customWidth="1" min="18" max="18"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="11" customWidth="1" min="14" max="14"/>
+    <col width="11" customWidth="1" min="15" max="15"/>
+    <col width="11" customWidth="1" min="16" max="16"/>
+    <col width="3" customWidth="1" min="18" max="18"/>
+    <col width="13" customWidth="1" min="19" max="19"/>
+    <col width="13" customWidth="1" min="20" max="20"/>
+    <col width="13" customWidth="1" min="21" max="21"/>
+    <col width="13" customWidth="1" min="22" max="22"/>
+    <col width="13" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1" ht="8" customHeight="1">
@@ -824,6 +831,11 @@
       <c r="Q1" s="1" t="n"/>
       <c r="R1" s="1" t="n"/>
       <c r="S1" s="1" t="n"/>
+      <c r="T1" s="1" t="n"/>
+      <c r="U1" s="1" t="n"/>
+      <c r="V1" s="1" t="n"/>
+      <c r="W1" s="1" t="n"/>
+      <c r="X1" s="1" t="n"/>
     </row>
     <row r="2" ht="26" customHeight="1">
       <c r="A2" s="1" t="n"/>
@@ -849,6 +861,11 @@
       <c r="Q2" s="1" t="n"/>
       <c r="R2" s="1" t="n"/>
       <c r="S2" s="1" t="n"/>
+      <c r="T2" s="1" t="n"/>
+      <c r="U2" s="1" t="n"/>
+      <c r="V2" s="1" t="n"/>
+      <c r="W2" s="1" t="n"/>
+      <c r="X2" s="1" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1">
       <c r="A3" s="1" t="n"/>
@@ -874,6 +891,11 @@
       <c r="Q3" s="1" t="n"/>
       <c r="R3" s="1" t="n"/>
       <c r="S3" s="1" t="n"/>
+      <c r="T3" s="1" t="n"/>
+      <c r="U3" s="1" t="n"/>
+      <c r="V3" s="1" t="n"/>
+      <c r="W3" s="1" t="n"/>
+      <c r="X3" s="1" t="n"/>
     </row>
     <row r="4" ht="8" customHeight="1">
       <c r="A4" s="4" t="n"/>
@@ -895,6 +917,11 @@
       <c r="Q4" s="4" t="n"/>
       <c r="R4" s="4" t="n"/>
       <c r="S4" s="4" t="n"/>
+      <c r="T4" s="4" t="n"/>
+      <c r="U4" s="4" t="n"/>
+      <c r="V4" s="4" t="n"/>
+      <c r="W4" s="4" t="n"/>
+      <c r="X4" s="4" t="n"/>
     </row>
     <row r="5" ht="17" customHeight="1">
       <c r="A5" s="4" t="n"/>
@@ -912,32 +939,37 @@
       <c r="I5" s="4" t="n"/>
       <c r="J5" s="4" t="n"/>
       <c r="K5" s="4" t="n"/>
-      <c r="L5" s="6" t="inlineStr">
+      <c r="L5" s="4" t="n"/>
+      <c r="M5" s="4" t="n"/>
+      <c r="N5" s="4" t="n"/>
+      <c r="O5" s="4" t="n"/>
+      <c r="P5" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">valeurs  </t>
         </is>
       </c>
-      <c r="M5" s="4" t="n"/>
-      <c r="N5" s="5" t="inlineStr">
+      <c r="Q5" s="4" t="n"/>
+      <c r="R5" s="4" t="n"/>
+      <c r="S5" s="5" t="inlineStr">
         <is>
           <t>Les cinq effets, calculés ici</t>
         </is>
       </c>
-      <c r="O5" s="4" t="n"/>
-      <c r="P5" s="4" t="n"/>
-      <c r="Q5" s="4" t="n"/>
-      <c r="R5" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">formules  </t>
-        </is>
-      </c>
-      <c r="S5" s="4" t="n"/>
+      <c r="T5" s="4" t="n"/>
+      <c r="U5" s="4" t="n"/>
+      <c r="V5" s="4" t="n"/>
+      <c r="W5" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">une multiplication chacun  </t>
+        </is>
+      </c>
+      <c r="X5" s="4" t="n"/>
     </row>
     <row r="6" ht="16" customHeight="1">
       <c r="A6" s="4" t="n"/>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>ENTITY</t>
+          <t>LIBELLE</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
@@ -952,71 +984,92 @@
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>CA_P</t>
+          <t>D_EFF</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>CA_N</t>
+          <t>CAE_P</t>
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>CVAR_P</t>
+          <t>CAE_N</t>
         </is>
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
-          <t>CVAR_N</t>
+          <t>CVE_P</t>
         </is>
       </c>
       <c r="I6" s="8" t="inlineStr">
         <is>
+          <t>CVE_N</t>
+        </is>
+      </c>
+      <c r="J6" s="8" t="inlineStr">
+        <is>
+          <t>MARGE_UNIT_P</t>
+        </is>
+      </c>
+      <c r="K6" s="8" t="inlineStr">
+        <is>
           <t>CDIR_P</t>
         </is>
       </c>
-      <c r="J6" s="8" t="inlineStr">
+      <c r="L6" s="8" t="inlineStr">
         <is>
           <t>CDIR_N</t>
         </is>
       </c>
-      <c r="K6" s="8" t="inlineStr">
+      <c r="M6" s="8" t="inlineStr">
         <is>
           <t>SIEGE_P</t>
         </is>
       </c>
-      <c r="L6" s="8" t="inlineStr">
+      <c r="N6" s="8" t="inlineStr">
         <is>
           <t>SIEGE_N</t>
         </is>
       </c>
-      <c r="M6" s="4" t="n"/>
-      <c r="N6" s="7" t="inlineStr">
+      <c r="O6" s="8" t="inlineStr">
+        <is>
+          <t>EBITDA_P</t>
+        </is>
+      </c>
+      <c r="P6" s="8" t="inlineStr">
+        <is>
+          <t>EBITDA_N</t>
+        </is>
+      </c>
+      <c r="Q6" s="4" t="n"/>
+      <c r="R6" s="4" t="n"/>
+      <c r="S6" s="7" t="inlineStr">
         <is>
           <t>Effectifs</t>
         </is>
       </c>
-      <c r="O6" s="8" t="inlineStr">
+      <c r="T6" s="8" t="inlineStr">
         <is>
           <t>Prix et mix</t>
         </is>
       </c>
-      <c r="P6" s="8" t="inlineStr">
+      <c r="U6" s="8" t="inlineStr">
         <is>
           <t>Coût var. unit.</t>
         </is>
       </c>
-      <c r="Q6" s="8" t="inlineStr">
+      <c r="V6" s="8" t="inlineStr">
         <is>
           <t>Coûts directs</t>
         </is>
       </c>
-      <c r="R6" s="8" t="inlineStr">
+      <c r="W6" s="8" t="inlineStr">
         <is>
           <t>Siège</t>
         </is>
       </c>
-      <c r="S6" s="4" t="n"/>
+      <c r="X6" s="4" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n"/>
@@ -1028,55 +1081,68 @@
       <c r="C7" s="10" t="n">
         <v>229</v>
       </c>
-      <c r="D7" s="11" t="n">
+      <c r="D7" s="10" t="n">
         <v>244</v>
       </c>
-      <c r="E7" s="11" t="n">
-        <v>1648000</v>
+      <c r="E7" s="10" t="n">
+        <v>15</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>1755850</v>
+        <v>7196.50655</v>
       </c>
       <c r="G7" s="11" t="n">
-        <v>224811</v>
+        <v>7196.106557</v>
       </c>
       <c r="H7" s="11" t="n">
-        <v>236740</v>
+        <v>981.7074239999999</v>
       </c>
       <c r="I7" s="11" t="n">
+        <v>970.245902</v>
+      </c>
+      <c r="J7" s="11" t="n">
+        <v>6214.799127</v>
+      </c>
+      <c r="K7" s="10" t="n">
         <v>901529.53</v>
       </c>
-      <c r="J7" s="11" t="n">
+      <c r="L7" s="10" t="n">
         <v>948506.29</v>
       </c>
-      <c r="K7" s="11" t="n">
+      <c r="M7" s="10" t="n">
         <v>261958.4339533122</v>
       </c>
-      <c r="L7" s="11" t="n">
+      <c r="N7" s="10" t="n">
         <v>280833.8246002989</v>
       </c>
-      <c r="M7" s="4" t="n"/>
-      <c r="N7" s="12">
-        <f>(D7-C7)*(E7/C7-G7/C7)</f>
-        <v/>
-      </c>
-      <c r="O7" s="12">
-        <f>(F7/D7-E7/C7)*D7</f>
-        <v/>
-      </c>
-      <c r="P7" s="12">
-        <f>-(H7/D7-G7/C7)*D7</f>
-        <v/>
-      </c>
-      <c r="Q7" s="12">
-        <f>-(J7-I7)</f>
-        <v/>
-      </c>
-      <c r="R7" s="12">
+      <c r="O7" s="10" t="n">
+        <v>259701.0360466878</v>
+      </c>
+      <c r="P7" s="10" t="n">
+        <v>289769.8853997011</v>
+      </c>
+      <c r="Q7" s="4" t="n"/>
+      <c r="R7" s="4" t="n"/>
+      <c r="S7" s="12">
+        <f>E7*J7</f>
+        <v/>
+      </c>
+      <c r="T7" s="12">
+        <f>(G7-F7)*D7</f>
+        <v/>
+      </c>
+      <c r="U7" s="12">
+        <f>-(I7-H7)*D7</f>
+        <v/>
+      </c>
+      <c r="V7" s="12">
         <f>-(L7-K7)</f>
         <v/>
       </c>
-      <c r="S7" s="4" t="n"/>
+      <c r="W7" s="12">
+        <f>-(N7-M7)</f>
+        <v/>
+      </c>
+      <c r="X7" s="4" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n"/>
@@ -1088,55 +1154,68 @@
       <c r="C8" s="10" t="n">
         <v>334</v>
       </c>
-      <c r="D8" s="11" t="n">
+      <c r="D8" s="10" t="n">
         <v>354</v>
       </c>
-      <c r="E8" s="11" t="n">
-        <v>2744480</v>
+      <c r="E8" s="10" t="n">
+        <v>20</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>2908720</v>
+        <v>8217.005988000001</v>
       </c>
       <c r="G8" s="11" t="n">
-        <v>353836</v>
+        <v>8216.723164000001</v>
       </c>
       <c r="H8" s="11" t="n">
-        <v>373616</v>
+        <v>1059.389222</v>
       </c>
       <c r="I8" s="11" t="n">
+        <v>1055.412429</v>
+      </c>
+      <c r="J8" s="11" t="n">
+        <v>7157.616766</v>
+      </c>
+      <c r="K8" s="10" t="n">
         <v>1532006.33</v>
       </c>
-      <c r="J8" s="11" t="n">
+      <c r="L8" s="10" t="n">
         <v>1601085.78</v>
       </c>
-      <c r="K8" s="11" t="n">
+      <c r="M8" s="10" t="n">
         <v>382070.6040951031</v>
       </c>
-      <c r="L8" s="11" t="n">
+      <c r="N8" s="10" t="n">
         <v>407439.4766752479</v>
       </c>
-      <c r="M8" s="4" t="n"/>
-      <c r="N8" s="12">
-        <f>(D8-C8)*(E8/C8-G8/C8)</f>
-        <v/>
-      </c>
-      <c r="O8" s="12">
-        <f>(F8/D8-E8/C8)*D8</f>
-        <v/>
-      </c>
-      <c r="P8" s="12">
-        <f>-(H8/D8-G8/C8)*D8</f>
-        <v/>
-      </c>
-      <c r="Q8" s="12">
-        <f>-(J8-I8)</f>
-        <v/>
-      </c>
-      <c r="R8" s="12">
+      <c r="O8" s="10" t="n">
+        <v>476567.0659048968</v>
+      </c>
+      <c r="P8" s="10" t="n">
+        <v>526578.7433247521</v>
+      </c>
+      <c r="Q8" s="4" t="n"/>
+      <c r="R8" s="4" t="n"/>
+      <c r="S8" s="12">
+        <f>E8*J8</f>
+        <v/>
+      </c>
+      <c r="T8" s="12">
+        <f>(G8-F8)*D8</f>
+        <v/>
+      </c>
+      <c r="U8" s="12">
+        <f>-(I8-H8)*D8</f>
+        <v/>
+      </c>
+      <c r="V8" s="12">
         <f>-(L8-K8)</f>
         <v/>
       </c>
-      <c r="S8" s="4" t="n"/>
+      <c r="W8" s="12">
+        <f>-(N8-M8)</f>
+        <v/>
+      </c>
+      <c r="X8" s="4" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n"/>
@@ -1148,55 +1227,68 @@
       <c r="C9" s="10" t="n">
         <v>216</v>
       </c>
-      <c r="D9" s="11" t="n">
+      <c r="D9" s="10" t="n">
         <v>231</v>
       </c>
-      <c r="E9" s="11" t="n">
-        <v>1522320</v>
+      <c r="E9" s="10" t="n">
+        <v>15</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>1627980</v>
+        <v>7047.777778</v>
       </c>
       <c r="G9" s="11" t="n">
-        <v>217343</v>
+        <v>7047.532468</v>
       </c>
       <c r="H9" s="11" t="n">
-        <v>228766</v>
+        <v>1006.217593</v>
       </c>
       <c r="I9" s="11" t="n">
+        <v>990.3290040000001</v>
+      </c>
+      <c r="J9" s="11" t="n">
+        <v>6041.560185</v>
+      </c>
+      <c r="K9" s="10" t="n">
         <v>822578.02</v>
       </c>
-      <c r="J9" s="11" t="n">
+      <c r="L9" s="10" t="n">
         <v>869560.28</v>
       </c>
-      <c r="K9" s="11" t="n">
+      <c r="M9" s="10" t="n">
         <v>247087.0060874675</v>
       </c>
-      <c r="L9" s="11" t="n">
+      <c r="N9" s="10" t="n">
         <v>265870.9093532066</v>
       </c>
-      <c r="M9" s="4" t="n"/>
-      <c r="N9" s="12">
-        <f>(D9-C9)*(E9/C9-G9/C9)</f>
-        <v/>
-      </c>
-      <c r="O9" s="12">
-        <f>(F9/D9-E9/C9)*D9</f>
-        <v/>
-      </c>
-      <c r="P9" s="12">
-        <f>-(H9/D9-G9/C9)*D9</f>
-        <v/>
-      </c>
-      <c r="Q9" s="12">
-        <f>-(J9-I9)</f>
-        <v/>
-      </c>
-      <c r="R9" s="12">
+      <c r="O9" s="10" t="n">
+        <v>235311.9739125325</v>
+      </c>
+      <c r="P9" s="10" t="n">
+        <v>263782.8106467934</v>
+      </c>
+      <c r="Q9" s="4" t="n"/>
+      <c r="R9" s="4" t="n"/>
+      <c r="S9" s="12">
+        <f>E9*J9</f>
+        <v/>
+      </c>
+      <c r="T9" s="12">
+        <f>(G9-F9)*D9</f>
+        <v/>
+      </c>
+      <c r="U9" s="12">
+        <f>-(I9-H9)*D9</f>
+        <v/>
+      </c>
+      <c r="V9" s="12">
         <f>-(L9-K9)</f>
         <v/>
       </c>
-      <c r="S9" s="4" t="n"/>
+      <c r="W9" s="12">
+        <f>-(N9-M9)</f>
+        <v/>
+      </c>
+      <c r="X9" s="4" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n"/>
@@ -1208,55 +1300,68 @@
       <c r="C10" s="10" t="n">
         <v>111</v>
       </c>
-      <c r="D10" s="11" t="n">
+      <c r="D10" s="10" t="n">
         <v>117</v>
       </c>
-      <c r="E10" s="11" t="n">
-        <v>741570</v>
+      <c r="E10" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>781650</v>
+        <v>6680.810811</v>
       </c>
       <c r="G10" s="11" t="n">
-        <v>124487</v>
+        <v>6680.769231</v>
       </c>
       <c r="H10" s="11" t="n">
-        <v>131151</v>
+        <v>1121.504505</v>
       </c>
       <c r="I10" s="11" t="n">
+        <v>1120.948718</v>
+      </c>
+      <c r="J10" s="11" t="n">
+        <v>5559.306306</v>
+      </c>
+      <c r="K10" s="10" t="n">
         <v>398826.0100000001</v>
       </c>
-      <c r="J10" s="11" t="n">
+      <c r="L10" s="10" t="n">
         <v>410605.25</v>
       </c>
-      <c r="K10" s="11" t="n">
+      <c r="M10" s="10" t="n">
         <v>124469.3147420315</v>
       </c>
-      <c r="L10" s="11" t="n">
+      <c r="N10" s="10" t="n">
         <v>132004.2356159417</v>
       </c>
-      <c r="M10" s="4" t="n"/>
-      <c r="N10" s="12">
-        <f>(D10-C10)*(E10/C10-G10/C10)</f>
-        <v/>
-      </c>
-      <c r="O10" s="12">
-        <f>(F10/D10-E10/C10)*D10</f>
-        <v/>
-      </c>
-      <c r="P10" s="12">
-        <f>-(H10/D10-G10/C10)*D10</f>
-        <v/>
-      </c>
-      <c r="Q10" s="12">
-        <f>-(J10-I10)</f>
-        <v/>
-      </c>
-      <c r="R10" s="12">
+      <c r="O10" s="10" t="n">
+        <v>93787.6752579684</v>
+      </c>
+      <c r="P10" s="10" t="n">
+        <v>107889.5143840583</v>
+      </c>
+      <c r="Q10" s="4" t="n"/>
+      <c r="R10" s="4" t="n"/>
+      <c r="S10" s="12">
+        <f>E10*J10</f>
+        <v/>
+      </c>
+      <c r="T10" s="12">
+        <f>(G10-F10)*D10</f>
+        <v/>
+      </c>
+      <c r="U10" s="12">
+        <f>-(I10-H10)*D10</f>
+        <v/>
+      </c>
+      <c r="V10" s="12">
         <f>-(L10-K10)</f>
         <v/>
       </c>
-      <c r="S10" s="4" t="n"/>
+      <c r="W10" s="12">
+        <f>-(N10-M10)</f>
+        <v/>
+      </c>
+      <c r="X10" s="4" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n"/>
@@ -1268,55 +1373,68 @@
       <c r="C11" s="10" t="n">
         <v>136</v>
       </c>
-      <c r="D11" s="11" t="n">
+      <c r="D11" s="10" t="n">
         <v>145</v>
       </c>
-      <c r="E11" s="11" t="n">
-        <v>956230</v>
+      <c r="E11" s="10" t="n">
+        <v>9</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>1019500</v>
+        <v>7031.102941</v>
       </c>
       <c r="G11" s="11" t="n">
-        <v>140414</v>
+        <v>7031.034483</v>
       </c>
       <c r="H11" s="11" t="n">
-        <v>148152</v>
+        <v>1032.455882</v>
       </c>
       <c r="I11" s="11" t="n">
+        <v>1021.737931</v>
+      </c>
+      <c r="J11" s="11" t="n">
+        <v>5998.647059</v>
+      </c>
+      <c r="K11" s="10" t="n">
         <v>533738.6800000001</v>
       </c>
-      <c r="J11" s="11" t="n">
+      <c r="L11" s="10" t="n">
         <v>557856.2</v>
       </c>
-      <c r="K11" s="11" t="n">
+      <c r="M11" s="10" t="n">
         <v>152502.7022939203</v>
       </c>
-      <c r="L11" s="11" t="n">
+      <c r="N11" s="10" t="n">
         <v>163594.7333690526</v>
       </c>
-      <c r="M11" s="4" t="n"/>
-      <c r="N11" s="12">
-        <f>(D11-C11)*(E11/C11-G11/C11)</f>
-        <v/>
-      </c>
-      <c r="O11" s="12">
-        <f>(F11/D11-E11/C11)*D11</f>
-        <v/>
-      </c>
-      <c r="P11" s="12">
-        <f>-(H11/D11-G11/C11)*D11</f>
-        <v/>
-      </c>
-      <c r="Q11" s="12">
-        <f>-(J11-I11)</f>
-        <v/>
-      </c>
-      <c r="R11" s="12">
+      <c r="O11" s="10" t="n">
+        <v>129574.6177060797</v>
+      </c>
+      <c r="P11" s="10" t="n">
+        <v>149897.0666309475</v>
+      </c>
+      <c r="Q11" s="4" t="n"/>
+      <c r="R11" s="4" t="n"/>
+      <c r="S11" s="12">
+        <f>E11*J11</f>
+        <v/>
+      </c>
+      <c r="T11" s="12">
+        <f>(G11-F11)*D11</f>
+        <v/>
+      </c>
+      <c r="U11" s="12">
+        <f>-(I11-H11)*D11</f>
+        <v/>
+      </c>
+      <c r="V11" s="12">
         <f>-(L11-K11)</f>
         <v/>
       </c>
-      <c r="S11" s="4" t="n"/>
+      <c r="W11" s="12">
+        <f>-(N11-M11)</f>
+        <v/>
+      </c>
+      <c r="X11" s="4" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n"/>
@@ -1328,55 +1446,68 @@
       <c r="C12" s="10" t="n">
         <v>111</v>
       </c>
-      <c r="D12" s="11" t="n">
+      <c r="D12" s="10" t="n">
         <v>117</v>
       </c>
-      <c r="E12" s="11" t="n">
-        <v>741570</v>
+      <c r="E12" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>781650</v>
+        <v>6680.810811</v>
       </c>
       <c r="G12" s="11" t="n">
-        <v>124264</v>
+        <v>6680.769231</v>
       </c>
       <c r="H12" s="11" t="n">
-        <v>130906</v>
+        <v>1119.495495</v>
       </c>
       <c r="I12" s="11" t="n">
+        <v>1118.854701</v>
+      </c>
+      <c r="J12" s="11" t="n">
+        <v>5561.315315</v>
+      </c>
+      <c r="K12" s="10" t="n">
         <v>399049.03</v>
       </c>
-      <c r="J12" s="11" t="n">
+      <c r="L12" s="10" t="n">
         <v>410850.2499999999</v>
       </c>
-      <c r="K12" s="11" t="n">
+      <c r="M12" s="10" t="n">
         <v>124469.3147420315</v>
       </c>
-      <c r="L12" s="11" t="n">
+      <c r="N12" s="10" t="n">
         <v>132004.2356159417</v>
       </c>
-      <c r="M12" s="4" t="n"/>
-      <c r="N12" s="12">
-        <f>(D12-C12)*(E12/C12-G12/C12)</f>
-        <v/>
-      </c>
-      <c r="O12" s="12">
-        <f>(F12/D12-E12/C12)*D12</f>
-        <v/>
-      </c>
-      <c r="P12" s="12">
-        <f>-(H12/D12-G12/C12)*D12</f>
-        <v/>
-      </c>
-      <c r="Q12" s="12">
-        <f>-(J12-I12)</f>
-        <v/>
-      </c>
-      <c r="R12" s="12">
+      <c r="O12" s="10" t="n">
+        <v>93787.65525796849</v>
+      </c>
+      <c r="P12" s="10" t="n">
+        <v>107889.5143840584</v>
+      </c>
+      <c r="Q12" s="4" t="n"/>
+      <c r="R12" s="4" t="n"/>
+      <c r="S12" s="12">
+        <f>E12*J12</f>
+        <v/>
+      </c>
+      <c r="T12" s="12">
+        <f>(G12-F12)*D12</f>
+        <v/>
+      </c>
+      <c r="U12" s="12">
+        <f>-(I12-H12)*D12</f>
+        <v/>
+      </c>
+      <c r="V12" s="12">
         <f>-(L12-K12)</f>
         <v/>
       </c>
-      <c r="S12" s="4" t="n"/>
+      <c r="W12" s="12">
+        <f>-(N12-M12)</f>
+        <v/>
+      </c>
+      <c r="X12" s="4" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n"/>
@@ -1388,55 +1519,68 @@
       <c r="C13" s="10" t="n">
         <v>234</v>
       </c>
-      <c r="D13" s="11" t="n">
+      <c r="D13" s="10" t="n">
         <v>249</v>
       </c>
-      <c r="E13" s="11" t="n">
-        <v>1666855</v>
+      <c r="E13" s="10" t="n">
+        <v>15</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>1773610</v>
+        <v>7123.311966</v>
       </c>
       <c r="G13" s="11" t="n">
-        <v>226316</v>
+        <v>7122.931727</v>
       </c>
       <c r="H13" s="11" t="n">
-        <v>238304</v>
+        <v>967.162393</v>
       </c>
       <c r="I13" s="11" t="n">
+        <v>957.044177</v>
+      </c>
+      <c r="J13" s="11" t="n">
+        <v>6156.149573</v>
+      </c>
+      <c r="K13" s="10" t="n">
         <v>901334.7799999998</v>
       </c>
-      <c r="J13" s="11" t="n">
+      <c r="L13" s="10" t="n">
         <v>943075.91</v>
       </c>
-      <c r="K13" s="11" t="n">
+      <c r="M13" s="10" t="n">
         <v>268151.2278180838</v>
       </c>
-      <c r="L13" s="11" t="n">
+      <c r="N13" s="10" t="n">
         <v>287095.221903666</v>
       </c>
-      <c r="M13" s="4" t="n"/>
-      <c r="N13" s="12">
-        <f>(D13-C13)*(E13/C13-G13/C13)</f>
-        <v/>
-      </c>
-      <c r="O13" s="12">
-        <f>(F13/D13-E13/C13)*D13</f>
-        <v/>
-      </c>
-      <c r="P13" s="12">
-        <f>-(H13/D13-G13/C13)*D13</f>
-        <v/>
-      </c>
-      <c r="Q13" s="12">
-        <f>-(J13-I13)</f>
-        <v/>
-      </c>
-      <c r="R13" s="12">
+      <c r="O13" s="10" t="n">
+        <v>271052.9921819164</v>
+      </c>
+      <c r="P13" s="10" t="n">
+        <v>305134.8680963339</v>
+      </c>
+      <c r="Q13" s="4" t="n"/>
+      <c r="R13" s="4" t="n"/>
+      <c r="S13" s="12">
+        <f>E13*J13</f>
+        <v/>
+      </c>
+      <c r="T13" s="12">
+        <f>(G13-F13)*D13</f>
+        <v/>
+      </c>
+      <c r="U13" s="12">
+        <f>-(I13-H13)*D13</f>
+        <v/>
+      </c>
+      <c r="V13" s="12">
         <f>-(L13-K13)</f>
         <v/>
       </c>
-      <c r="S13" s="4" t="n"/>
+      <c r="W13" s="12">
+        <f>-(N13-M13)</f>
+        <v/>
+      </c>
+      <c r="X13" s="4" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n"/>
@@ -1448,55 +1592,68 @@
       <c r="C14" s="10" t="n">
         <v>304</v>
       </c>
-      <c r="D14" s="11" t="n">
+      <c r="D14" s="10" t="n">
         <v>324</v>
       </c>
-      <c r="E14" s="11" t="n">
-        <v>2342685</v>
+      <c r="E14" s="10" t="n">
+        <v>20</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>2496705</v>
+        <v>7706.200658</v>
       </c>
       <c r="G14" s="11" t="n">
-        <v>302850</v>
+        <v>7705.87963</v>
       </c>
       <c r="H14" s="11" t="n">
-        <v>319290</v>
+        <v>996.2171049999999</v>
       </c>
       <c r="I14" s="11" t="n">
+        <v>985.4629629999999</v>
+      </c>
+      <c r="J14" s="11" t="n">
+        <v>6709.983553</v>
+      </c>
+      <c r="K14" s="10" t="n">
         <v>1284681.03</v>
       </c>
-      <c r="J14" s="11" t="n">
+      <c r="L14" s="10" t="n">
         <v>1346872.36</v>
       </c>
-      <c r="K14" s="11" t="n">
+      <c r="M14" s="10" t="n">
         <v>348367.1950673439</v>
       </c>
-      <c r="L14" s="11" t="n">
+      <c r="N14" s="10" t="n">
         <v>373569.4589820922</v>
       </c>
-      <c r="M14" s="4" t="n"/>
-      <c r="N14" s="12">
-        <f>(D14-C14)*(E14/C14-G14/C14)</f>
-        <v/>
-      </c>
-      <c r="O14" s="12">
-        <f>(F14/D14-E14/C14)*D14</f>
-        <v/>
-      </c>
-      <c r="P14" s="12">
-        <f>-(H14/D14-G14/C14)*D14</f>
-        <v/>
-      </c>
-      <c r="Q14" s="12">
-        <f>-(J14-I14)</f>
-        <v/>
-      </c>
-      <c r="R14" s="12">
+      <c r="O14" s="10" t="n">
+        <v>406786.7749326563</v>
+      </c>
+      <c r="P14" s="10" t="n">
+        <v>456973.1810179077</v>
+      </c>
+      <c r="Q14" s="4" t="n"/>
+      <c r="R14" s="4" t="n"/>
+      <c r="S14" s="12">
+        <f>E14*J14</f>
+        <v/>
+      </c>
+      <c r="T14" s="12">
+        <f>(G14-F14)*D14</f>
+        <v/>
+      </c>
+      <c r="U14" s="12">
+        <f>-(I14-H14)*D14</f>
+        <v/>
+      </c>
+      <c r="V14" s="12">
         <f>-(L14-K14)</f>
         <v/>
       </c>
-      <c r="S14" s="4" t="n"/>
+      <c r="W14" s="12">
+        <f>-(N14-M14)</f>
+        <v/>
+      </c>
+      <c r="X14" s="4" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n"/>
@@ -1508,55 +1665,68 @@
       <c r="C15" s="10" t="n">
         <v>279</v>
       </c>
-      <c r="D15" s="11" t="n">
+      <c r="D15" s="10" t="n">
         <v>294</v>
       </c>
-      <c r="E15" s="11" t="n">
-        <v>2048260</v>
+      <c r="E15" s="10" t="n">
+        <v>15</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>2158300</v>
+        <v>7341.433692</v>
       </c>
       <c r="G15" s="11" t="n">
-        <v>271353</v>
+        <v>7341.156463</v>
       </c>
       <c r="H15" s="11" t="n">
-        <v>285804</v>
+        <v>972.591398</v>
       </c>
       <c r="I15" s="11" t="n">
+        <v>972.122449</v>
+      </c>
+      <c r="J15" s="11" t="n">
+        <v>6368.842294</v>
+      </c>
+      <c r="K15" s="10" t="n">
         <v>1111778.52</v>
       </c>
-      <c r="J15" s="11" t="n">
+      <c r="L15" s="10" t="n">
         <v>1149246.53</v>
       </c>
-      <c r="K15" s="11" t="n">
+      <c r="M15" s="10" t="n">
         <v>319718.4864015467</v>
       </c>
-      <c r="L15" s="11" t="n">
+      <c r="N15" s="10" t="n">
         <v>338979.5981499978</v>
       </c>
-      <c r="M15" s="4" t="n"/>
-      <c r="N15" s="12">
-        <f>(D15-C15)*(E15/C15-G15/C15)</f>
-        <v/>
-      </c>
-      <c r="O15" s="12">
-        <f>(F15/D15-E15/C15)*D15</f>
-        <v/>
-      </c>
-      <c r="P15" s="12">
-        <f>-(H15/D15-G15/C15)*D15</f>
-        <v/>
-      </c>
-      <c r="Q15" s="12">
-        <f>-(J15-I15)</f>
-        <v/>
-      </c>
-      <c r="R15" s="12">
+      <c r="O15" s="10" t="n">
+        <v>345409.9935984532</v>
+      </c>
+      <c r="P15" s="10" t="n">
+        <v>384269.8718500021</v>
+      </c>
+      <c r="Q15" s="4" t="n"/>
+      <c r="R15" s="4" t="n"/>
+      <c r="S15" s="12">
+        <f>E15*J15</f>
+        <v/>
+      </c>
+      <c r="T15" s="12">
+        <f>(G15-F15)*D15</f>
+        <v/>
+      </c>
+      <c r="U15" s="12">
+        <f>-(I15-H15)*D15</f>
+        <v/>
+      </c>
+      <c r="V15" s="12">
         <f>-(L15-K15)</f>
         <v/>
       </c>
-      <c r="S15" s="4" t="n"/>
+      <c r="W15" s="12">
+        <f>-(N15-M15)</f>
+        <v/>
+      </c>
+      <c r="X15" s="4" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n"/>
@@ -1568,55 +1738,68 @@
       <c r="C16" s="10" t="n">
         <v>362</v>
       </c>
-      <c r="D16" s="11" t="n">
+      <c r="D16" s="10" t="n">
         <v>382</v>
       </c>
-      <c r="E16" s="11" t="n">
-        <v>2974600</v>
+      <c r="E16" s="10" t="n">
+        <v>20</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>3138840</v>
+        <v>8217.127071999999</v>
       </c>
       <c r="G16" s="11" t="n">
-        <v>370591</v>
+        <v>8216.858639</v>
       </c>
       <c r="H16" s="11" t="n">
-        <v>391525</v>
+        <v>1023.732044</v>
       </c>
       <c r="I16" s="11" t="n">
+        <v>1024.934555</v>
+      </c>
+      <c r="J16" s="11" t="n">
+        <v>7193.395028</v>
+      </c>
+      <c r="K16" s="10" t="n">
         <v>1648776.64</v>
       </c>
-      <c r="J16" s="11" t="n">
+      <c r="L16" s="10" t="n">
         <v>1707251.49</v>
       </c>
-      <c r="K16" s="11" t="n">
+      <c r="M16" s="10" t="n">
         <v>414832.3340357959</v>
       </c>
-      <c r="L16" s="11" t="n">
+      <c r="N16" s="10" t="n">
         <v>440443.3705915956</v>
       </c>
-      <c r="M16" s="4" t="n"/>
-      <c r="N16" s="12">
-        <f>(D16-C16)*(E16/C16-G16/C16)</f>
-        <v/>
-      </c>
-      <c r="O16" s="12">
-        <f>(F16/D16-E16/C16)*D16</f>
-        <v/>
-      </c>
-      <c r="P16" s="12">
-        <f>-(H16/D16-G16/C16)*D16</f>
-        <v/>
-      </c>
-      <c r="Q16" s="12">
-        <f>-(J16-I16)</f>
-        <v/>
-      </c>
-      <c r="R16" s="12">
+      <c r="O16" s="10" t="n">
+        <v>540400.0259642038</v>
+      </c>
+      <c r="P16" s="10" t="n">
+        <v>599620.1394084045</v>
+      </c>
+      <c r="Q16" s="4" t="n"/>
+      <c r="R16" s="4" t="n"/>
+      <c r="S16" s="12">
+        <f>E16*J16</f>
+        <v/>
+      </c>
+      <c r="T16" s="12">
+        <f>(G16-F16)*D16</f>
+        <v/>
+      </c>
+      <c r="U16" s="12">
+        <f>-(I16-H16)*D16</f>
+        <v/>
+      </c>
+      <c r="V16" s="12">
         <f>-(L16-K16)</f>
         <v/>
       </c>
-      <c r="S16" s="4" t="n"/>
+      <c r="W16" s="12">
+        <f>-(N16-M16)</f>
+        <v/>
+      </c>
+      <c r="X16" s="4" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n"/>
@@ -1628,55 +1811,68 @@
       <c r="C17" s="10" t="n">
         <v>166</v>
       </c>
-      <c r="D17" s="11" t="n">
+      <c r="D17" s="10" t="n">
         <v>176</v>
       </c>
-      <c r="E17" s="11" t="n">
-        <v>1068270</v>
+      <c r="E17" s="10" t="n">
+        <v>10</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>1132650</v>
+        <v>6435.361446</v>
       </c>
       <c r="G17" s="11" t="n">
-        <v>162584</v>
+        <v>6435.511364</v>
       </c>
       <c r="H17" s="11" t="n">
-        <v>171389</v>
+        <v>979.421687</v>
       </c>
       <c r="I17" s="11" t="n">
+        <v>973.801136</v>
+      </c>
+      <c r="J17" s="11" t="n">
+        <v>5455.939759</v>
+      </c>
+      <c r="K17" s="10" t="n">
         <v>508701.5699999999</v>
       </c>
-      <c r="J17" s="11" t="n">
+      <c r="L17" s="10" t="n">
         <v>530872.76</v>
       </c>
-      <c r="K17" s="11" t="n">
+      <c r="M17" s="10" t="n">
         <v>185745.8159994536</v>
       </c>
-      <c r="L17" s="11" t="n">
+      <c r="N17" s="10" t="n">
         <v>198146.4540348334</v>
       </c>
-      <c r="M17" s="4" t="n"/>
-      <c r="N17" s="12">
-        <f>(D17-C17)*(E17/C17-G17/C17)</f>
-        <v/>
-      </c>
-      <c r="O17" s="12">
-        <f>(F17/D17-E17/C17)*D17</f>
-        <v/>
-      </c>
-      <c r="P17" s="12">
-        <f>-(H17/D17-G17/C17)*D17</f>
-        <v/>
-      </c>
-      <c r="Q17" s="12">
-        <f>-(J17-I17)</f>
-        <v/>
-      </c>
-      <c r="R17" s="12">
+      <c r="O17" s="10" t="n">
+        <v>211238.6140005465</v>
+      </c>
+      <c r="P17" s="10" t="n">
+        <v>232241.7859651666</v>
+      </c>
+      <c r="Q17" s="4" t="n"/>
+      <c r="R17" s="4" t="n"/>
+      <c r="S17" s="12">
+        <f>E17*J17</f>
+        <v/>
+      </c>
+      <c r="T17" s="12">
+        <f>(G17-F17)*D17</f>
+        <v/>
+      </c>
+      <c r="U17" s="12">
+        <f>-(I17-H17)*D17</f>
+        <v/>
+      </c>
+      <c r="V17" s="12">
         <f>-(L17-K17)</f>
         <v/>
       </c>
-      <c r="S17" s="4" t="n"/>
+      <c r="W17" s="12">
+        <f>-(N17-M17)</f>
+        <v/>
+      </c>
+      <c r="X17" s="4" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n"/>
@@ -1688,55 +1884,68 @@
       <c r="C18" s="10" t="n">
         <v>211</v>
       </c>
-      <c r="D18" s="11" t="n">
+      <c r="D18" s="10" t="n">
         <v>226</v>
       </c>
-      <c r="E18" s="11" t="n">
-        <v>1469340</v>
+      <c r="E18" s="10" t="n">
+        <v>15</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>1573830</v>
+        <v>6963.696682</v>
       </c>
       <c r="G18" s="11" t="n">
-        <v>190103</v>
+        <v>6963.849558</v>
       </c>
       <c r="H18" s="11" t="n">
-        <v>200917</v>
+        <v>900.962085</v>
       </c>
       <c r="I18" s="11" t="n">
+        <v>889.013274</v>
+      </c>
+      <c r="J18" s="11" t="n">
+        <v>6062.734597</v>
+      </c>
+      <c r="K18" s="10" t="n">
         <v>736369.5600000001</v>
       </c>
-      <c r="J18" s="11" t="n">
+      <c r="L18" s="10" t="n">
         <v>778456.91</v>
       </c>
-      <c r="K18" s="11" t="n">
+      <c r="M18" s="10" t="n">
         <v>236099.0885076113</v>
       </c>
-      <c r="L18" s="11" t="n">
+      <c r="N18" s="10" t="n">
         <v>254438.5895015823</v>
       </c>
-      <c r="M18" s="4" t="n"/>
-      <c r="N18" s="12">
-        <f>(D18-C18)*(E18/C18-G18/C18)</f>
-        <v/>
-      </c>
-      <c r="O18" s="12">
-        <f>(F18/D18-E18/C18)*D18</f>
-        <v/>
-      </c>
-      <c r="P18" s="12">
-        <f>-(H18/D18-G18/C18)*D18</f>
-        <v/>
-      </c>
-      <c r="Q18" s="12">
-        <f>-(J18-I18)</f>
-        <v/>
-      </c>
-      <c r="R18" s="12">
+      <c r="O18" s="10" t="n">
+        <v>306768.3514923886</v>
+      </c>
+      <c r="P18" s="10" t="n">
+        <v>340017.5004984176</v>
+      </c>
+      <c r="Q18" s="4" t="n"/>
+      <c r="R18" s="4" t="n"/>
+      <c r="S18" s="12">
+        <f>E18*J18</f>
+        <v/>
+      </c>
+      <c r="T18" s="12">
+        <f>(G18-F18)*D18</f>
+        <v/>
+      </c>
+      <c r="U18" s="12">
+        <f>-(I18-H18)*D18</f>
+        <v/>
+      </c>
+      <c r="V18" s="12">
         <f>-(L18-K18)</f>
         <v/>
       </c>
-      <c r="S18" s="4" t="n"/>
+      <c r="W18" s="12">
+        <f>-(N18-M18)</f>
+        <v/>
+      </c>
+      <c r="X18" s="4" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n"/>
@@ -1748,55 +1957,68 @@
       <c r="C19" s="10" t="n">
         <v>111</v>
       </c>
-      <c r="D19" s="11" t="n">
+      <c r="D19" s="10" t="n">
         <v>117</v>
       </c>
-      <c r="E19" s="11" t="n">
-        <v>819270</v>
+      <c r="E19" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>863550</v>
+        <v>7380.810811</v>
       </c>
       <c r="G19" s="11" t="n">
-        <v>127825</v>
+        <v>7380.769231</v>
       </c>
       <c r="H19" s="11" t="n">
-        <v>134823</v>
+        <v>1151.576577</v>
       </c>
       <c r="I19" s="11" t="n">
+        <v>1152.333333</v>
+      </c>
+      <c r="J19" s="11" t="n">
+        <v>6229.234234</v>
+      </c>
+      <c r="K19" s="10" t="n">
         <v>523989.18</v>
       </c>
-      <c r="J19" s="11" t="n">
+      <c r="L19" s="10" t="n">
         <v>561046.28</v>
       </c>
-      <c r="K19" s="11" t="n">
+      <c r="M19" s="10" t="n">
         <v>127153.9396992599</v>
       </c>
-      <c r="L19" s="11" t="n">
+      <c r="N19" s="10" t="n">
         <v>134851.3780311536</v>
       </c>
-      <c r="M19" s="4" t="n"/>
-      <c r="N19" s="12">
-        <f>(D19-C19)*(E19/C19-G19/C19)</f>
-        <v/>
-      </c>
-      <c r="O19" s="12">
-        <f>(F19/D19-E19/C19)*D19</f>
-        <v/>
-      </c>
-      <c r="P19" s="12">
-        <f>-(H19/D19-G19/C19)*D19</f>
-        <v/>
-      </c>
-      <c r="Q19" s="12">
-        <f>-(J19-I19)</f>
-        <v/>
-      </c>
-      <c r="R19" s="12">
+      <c r="O19" s="10" t="n">
+        <v>40301.88030074014</v>
+      </c>
+      <c r="P19" s="10" t="n">
+        <v>32829.34196884636</v>
+      </c>
+      <c r="Q19" s="4" t="n"/>
+      <c r="R19" s="4" t="n"/>
+      <c r="S19" s="12">
+        <f>E19*J19</f>
+        <v/>
+      </c>
+      <c r="T19" s="12">
+        <f>(G19-F19)*D19</f>
+        <v/>
+      </c>
+      <c r="U19" s="12">
+        <f>-(I19-H19)*D19</f>
+        <v/>
+      </c>
+      <c r="V19" s="12">
         <f>-(L19-K19)</f>
         <v/>
       </c>
-      <c r="S19" s="4" t="n"/>
+      <c r="W19" s="12">
+        <f>-(N19-M19)</f>
+        <v/>
+      </c>
+      <c r="X19" s="4" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n"/>
@@ -1808,55 +2030,68 @@
       <c r="C20" s="10" t="n">
         <v>129</v>
       </c>
-      <c r="D20" s="11" t="n">
+      <c r="D20" s="10" t="n">
         <v>138</v>
       </c>
-      <c r="E20" s="11" t="n">
-        <v>1015320</v>
+      <c r="E20" s="10" t="n">
+        <v>9</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>1086150</v>
+        <v>7870.697674</v>
       </c>
       <c r="G20" s="11" t="n">
-        <v>145638</v>
+        <v>7870.652174</v>
       </c>
       <c r="H20" s="11" t="n">
-        <v>154027</v>
+        <v>1128.976744</v>
       </c>
       <c r="I20" s="11" t="n">
+        <v>1116.137681</v>
+      </c>
+      <c r="J20" s="11" t="n">
+        <v>6741.72093</v>
+      </c>
+      <c r="K20" s="10" t="n">
         <v>664829.1599999999</v>
       </c>
-      <c r="J20" s="11" t="n">
+      <c r="L20" s="10" t="n">
         <v>724171.6999999998</v>
       </c>
-      <c r="K20" s="11" t="n">
+      <c r="M20" s="10" t="n">
         <v>147773.5365570392</v>
       </c>
-      <c r="L20" s="11" t="n">
+      <c r="N20" s="10" t="n">
         <v>159055.5135753902</v>
       </c>
-      <c r="M20" s="4" t="n"/>
-      <c r="N20" s="12">
-        <f>(D20-C20)*(E20/C20-G20/C20)</f>
-        <v/>
-      </c>
-      <c r="O20" s="12">
-        <f>(F20/D20-E20/C20)*D20</f>
-        <v/>
-      </c>
-      <c r="P20" s="12">
-        <f>-(H20/D20-G20/C20)*D20</f>
-        <v/>
-      </c>
-      <c r="Q20" s="12">
-        <f>-(J20-I20)</f>
-        <v/>
-      </c>
-      <c r="R20" s="12">
+      <c r="O20" s="10" t="n">
+        <v>57079.30344296087</v>
+      </c>
+      <c r="P20" s="10" t="n">
+        <v>48895.78642460998</v>
+      </c>
+      <c r="Q20" s="4" t="n"/>
+      <c r="R20" s="4" t="n"/>
+      <c r="S20" s="12">
+        <f>E20*J20</f>
+        <v/>
+      </c>
+      <c r="T20" s="12">
+        <f>(G20-F20)*D20</f>
+        <v/>
+      </c>
+      <c r="U20" s="12">
+        <f>-(I20-H20)*D20</f>
+        <v/>
+      </c>
+      <c r="V20" s="12">
         <f>-(L20-K20)</f>
         <v/>
       </c>
-      <c r="S20" s="4" t="n"/>
+      <c r="W20" s="12">
+        <f>-(N20-M20)</f>
+        <v/>
+      </c>
+      <c r="X20" s="4" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n"/>
@@ -1877,26 +2112,11 @@
         <f>SUM(E7:E20)</f>
         <v/>
       </c>
-      <c r="F21" s="14">
-        <f>SUM(F7:F20)</f>
-        <v/>
-      </c>
-      <c r="G21" s="14">
-        <f>SUM(G7:G20)</f>
-        <v/>
-      </c>
-      <c r="H21" s="14">
-        <f>SUM(H7:H20)</f>
-        <v/>
-      </c>
-      <c r="I21" s="14">
-        <f>SUM(I7:I20)</f>
-        <v/>
-      </c>
-      <c r="J21" s="14">
-        <f>SUM(J7:J20)</f>
-        <v/>
-      </c>
+      <c r="F21" s="4" t="n"/>
+      <c r="G21" s="4" t="n"/>
+      <c r="H21" s="4" t="n"/>
+      <c r="I21" s="4" t="n"/>
+      <c r="J21" s="4" t="n"/>
       <c r="K21" s="14">
         <f>SUM(K7:K20)</f>
         <v/>
@@ -1905,7 +2125,10 @@
         <f>SUM(L7:L20)</f>
         <v/>
       </c>
-      <c r="M21" s="4" t="n"/>
+      <c r="M21" s="14">
+        <f>SUM(M7:M20)</f>
+        <v/>
+      </c>
       <c r="N21" s="14">
         <f>SUM(N7:N20)</f>
         <v/>
@@ -1918,15 +2141,29 @@
         <f>SUM(P7:P20)</f>
         <v/>
       </c>
-      <c r="Q21" s="14">
-        <f>SUM(Q7:Q20)</f>
-        <v/>
-      </c>
-      <c r="R21" s="14">
-        <f>SUM(R7:R20)</f>
-        <v/>
-      </c>
-      <c r="S21" s="4" t="n"/>
+      <c r="Q21" s="4" t="n"/>
+      <c r="R21" s="4" t="n"/>
+      <c r="S21" s="14">
+        <f>SUM(S7:S20)</f>
+        <v/>
+      </c>
+      <c r="T21" s="14">
+        <f>SUM(T7:T20)</f>
+        <v/>
+      </c>
+      <c r="U21" s="14">
+        <f>SUM(U7:U20)</f>
+        <v/>
+      </c>
+      <c r="V21" s="14">
+        <f>SUM(V7:V20)</f>
+        <v/>
+      </c>
+      <c r="W21" s="14">
+        <f>SUM(W7:W20)</f>
+        <v/>
+      </c>
+      <c r="X21" s="4" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="4" t="n"/>
@@ -1948,6 +2185,11 @@
       <c r="Q22" s="4" t="n"/>
       <c r="R22" s="4" t="n"/>
       <c r="S22" s="4" t="n"/>
+      <c r="T22" s="4" t="n"/>
+      <c r="U22" s="4" t="n"/>
+      <c r="V22" s="4" t="n"/>
+      <c r="W22" s="4" t="n"/>
+      <c r="X22" s="4" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="4" t="n"/>
@@ -1985,6 +2227,11 @@
       <c r="Q23" s="4" t="n"/>
       <c r="R23" s="4" t="n"/>
       <c r="S23" s="4" t="n"/>
+      <c r="T23" s="4" t="n"/>
+      <c r="U23" s="4" t="n"/>
+      <c r="V23" s="4" t="n"/>
+      <c r="W23" s="4" t="n"/>
+      <c r="X23" s="4" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="4" t="n"/>
@@ -2042,6 +2289,11 @@
       <c r="Q24" s="4" t="n"/>
       <c r="R24" s="4" t="n"/>
       <c r="S24" s="4" t="n"/>
+      <c r="T24" s="4" t="n"/>
+      <c r="U24" s="4" t="n"/>
+      <c r="V24" s="4" t="n"/>
+      <c r="W24" s="4" t="n"/>
+      <c r="X24" s="4" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="4" t="n"/>
@@ -2054,7 +2306,7 @@
         </is>
       </c>
       <c r="D25" s="17">
-        <f>SUM(E7:E20)-SUM(G7:G20)-SUM(I7:I20)-SUM(K7:K20)</f>
+        <f>SUM(O7:O20)</f>
         <v/>
       </c>
       <c r="E25" s="18" t="n"/>
@@ -2085,43 +2337,48 @@
       <c r="Q25" s="4" t="n"/>
       <c r="R25" s="4" t="n"/>
       <c r="S25" s="4" t="n"/>
+      <c r="T25" s="4" t="n"/>
+      <c r="U25" s="4" t="n"/>
+      <c r="V25" s="4" t="n"/>
+      <c r="W25" s="4" t="n"/>
+      <c r="X25" s="4" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="4" t="n"/>
       <c r="B26" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="C26" s="9" t="inlineStr">
+      <c r="C26" s="22" t="inlineStr">
         <is>
           <t>Effet effectifs</t>
         </is>
       </c>
-      <c r="D26" s="22">
-        <f>N21</f>
-        <v/>
-      </c>
-      <c r="E26" s="23">
+      <c r="D26" s="23">
+        <f>S21</f>
+        <v/>
+      </c>
+      <c r="E26" s="24">
         <f>IFERROR(D26/(D31-D25),"")</f>
         <v/>
       </c>
       <c r="F26" s="4" t="n"/>
-      <c r="G26" s="9" t="inlineStr">
+      <c r="G26" s="22" t="inlineStr">
         <is>
           <t>Effet effectifs</t>
         </is>
       </c>
-      <c r="H26" s="11">
+      <c r="H26" s="10">
         <f>MIN(D25,D25+SUM(D26:D26))</f>
         <v/>
       </c>
-      <c r="I26" s="11" t="n">
+      <c r="I26" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="J26" s="11">
+      <c r="J26" s="10">
         <f>MAX(D26,0)</f>
         <v/>
       </c>
-      <c r="K26" s="11">
+      <c r="K26" s="10">
         <f>MAX(-D26,0)</f>
         <v/>
       </c>
@@ -2133,43 +2390,48 @@
       <c r="Q26" s="4" t="n"/>
       <c r="R26" s="4" t="n"/>
       <c r="S26" s="4" t="n"/>
+      <c r="T26" s="4" t="n"/>
+      <c r="U26" s="4" t="n"/>
+      <c r="V26" s="4" t="n"/>
+      <c r="W26" s="4" t="n"/>
+      <c r="X26" s="4" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="4" t="n"/>
       <c r="B27" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="C27" s="9" t="inlineStr">
+      <c r="C27" s="22" t="inlineStr">
         <is>
           <t>Effet prix et mix</t>
         </is>
       </c>
-      <c r="D27" s="22">
-        <f>O21</f>
-        <v/>
-      </c>
-      <c r="E27" s="23">
+      <c r="D27" s="23">
+        <f>T21</f>
+        <v/>
+      </c>
+      <c r="E27" s="24">
         <f>IFERROR(D27/(D31-D25),"")</f>
         <v/>
       </c>
       <c r="F27" s="4" t="n"/>
-      <c r="G27" s="9" t="inlineStr">
+      <c r="G27" s="22" t="inlineStr">
         <is>
           <t>Effet prix et mix</t>
         </is>
       </c>
-      <c r="H27" s="11">
+      <c r="H27" s="10">
         <f>MIN(D25+SUM(D26:D26),D25+SUM(D26:D27))</f>
         <v/>
       </c>
-      <c r="I27" s="11" t="n">
+      <c r="I27" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="J27" s="11">
+      <c r="J27" s="10">
         <f>MAX(D27,0)</f>
         <v/>
       </c>
-      <c r="K27" s="11">
+      <c r="K27" s="10">
         <f>MAX(-D27,0)</f>
         <v/>
       </c>
@@ -2181,43 +2443,48 @@
       <c r="Q27" s="4" t="n"/>
       <c r="R27" s="4" t="n"/>
       <c r="S27" s="4" t="n"/>
+      <c r="T27" s="4" t="n"/>
+      <c r="U27" s="4" t="n"/>
+      <c r="V27" s="4" t="n"/>
+      <c r="W27" s="4" t="n"/>
+      <c r="X27" s="4" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="4" t="n"/>
       <c r="B28" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="C28" s="9" t="inlineStr">
+      <c r="C28" s="22" t="inlineStr">
         <is>
           <t>Effet coût var. unitaire</t>
         </is>
       </c>
-      <c r="D28" s="22">
-        <f>P21</f>
-        <v/>
-      </c>
-      <c r="E28" s="23">
+      <c r="D28" s="23">
+        <f>U21</f>
+        <v/>
+      </c>
+      <c r="E28" s="24">
         <f>IFERROR(D28/(D31-D25),"")</f>
         <v/>
       </c>
       <c r="F28" s="4" t="n"/>
-      <c r="G28" s="9" t="inlineStr">
+      <c r="G28" s="22" t="inlineStr">
         <is>
           <t>Effet coût var. unitaire</t>
         </is>
       </c>
-      <c r="H28" s="11">
+      <c r="H28" s="10">
         <f>MIN(D25+SUM(D26:D27),D25+SUM(D26:D28))</f>
         <v/>
       </c>
-      <c r="I28" s="11" t="n">
+      <c r="I28" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="J28" s="11">
+      <c r="J28" s="10">
         <f>MAX(D28,0)</f>
         <v/>
       </c>
-      <c r="K28" s="11">
+      <c r="K28" s="10">
         <f>MAX(-D28,0)</f>
         <v/>
       </c>
@@ -2229,43 +2496,48 @@
       <c r="Q28" s="4" t="n"/>
       <c r="R28" s="4" t="n"/>
       <c r="S28" s="4" t="n"/>
+      <c r="T28" s="4" t="n"/>
+      <c r="U28" s="4" t="n"/>
+      <c r="V28" s="4" t="n"/>
+      <c r="W28" s="4" t="n"/>
+      <c r="X28" s="4" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="4" t="n"/>
       <c r="B29" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="C29" s="9" t="inlineStr">
+      <c r="C29" s="22" t="inlineStr">
         <is>
           <t>Effet coûts directs</t>
         </is>
       </c>
-      <c r="D29" s="22">
-        <f>Q21</f>
-        <v/>
-      </c>
-      <c r="E29" s="23">
+      <c r="D29" s="23">
+        <f>V21</f>
+        <v/>
+      </c>
+      <c r="E29" s="24">
         <f>IFERROR(D29/(D31-D25),"")</f>
         <v/>
       </c>
       <c r="F29" s="4" t="n"/>
-      <c r="G29" s="9" t="inlineStr">
+      <c r="G29" s="22" t="inlineStr">
         <is>
           <t>Effet coûts directs</t>
         </is>
       </c>
-      <c r="H29" s="11">
+      <c r="H29" s="10">
         <f>MIN(D25+SUM(D26:D28),D25+SUM(D26:D29))</f>
         <v/>
       </c>
-      <c r="I29" s="11" t="n">
+      <c r="I29" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="J29" s="11">
+      <c r="J29" s="10">
         <f>MAX(D29,0)</f>
         <v/>
       </c>
-      <c r="K29" s="11">
+      <c r="K29" s="10">
         <f>MAX(-D29,0)</f>
         <v/>
       </c>
@@ -2277,43 +2549,48 @@
       <c r="Q29" s="4" t="n"/>
       <c r="R29" s="4" t="n"/>
       <c r="S29" s="4" t="n"/>
+      <c r="T29" s="4" t="n"/>
+      <c r="U29" s="4" t="n"/>
+      <c r="V29" s="4" t="n"/>
+      <c r="W29" s="4" t="n"/>
+      <c r="X29" s="4" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="4" t="n"/>
       <c r="B30" s="21" t="n">
         <v>6</v>
       </c>
-      <c r="C30" s="9" t="inlineStr">
+      <c r="C30" s="22" t="inlineStr">
         <is>
           <t>Effet siège</t>
         </is>
       </c>
-      <c r="D30" s="22">
-        <f>R21</f>
-        <v/>
-      </c>
-      <c r="E30" s="23">
+      <c r="D30" s="23">
+        <f>W21</f>
+        <v/>
+      </c>
+      <c r="E30" s="24">
         <f>IFERROR(D30/(D31-D25),"")</f>
         <v/>
       </c>
       <c r="F30" s="4" t="n"/>
-      <c r="G30" s="9" t="inlineStr">
+      <c r="G30" s="22" t="inlineStr">
         <is>
           <t>Effet siège</t>
         </is>
       </c>
-      <c r="H30" s="11">
+      <c r="H30" s="10">
         <f>MIN(D25+SUM(D26:D29),D25+SUM(D26:D30))</f>
         <v/>
       </c>
-      <c r="I30" s="11" t="n">
+      <c r="I30" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="J30" s="11">
+      <c r="J30" s="10">
         <f>MAX(D30,0)</f>
         <v/>
       </c>
-      <c r="K30" s="11">
+      <c r="K30" s="10">
         <f>MAX(-D30,0)</f>
         <v/>
       </c>
@@ -2325,6 +2602,11 @@
       <c r="Q30" s="4" t="n"/>
       <c r="R30" s="4" t="n"/>
       <c r="S30" s="4" t="n"/>
+      <c r="T30" s="4" t="n"/>
+      <c r="U30" s="4" t="n"/>
+      <c r="V30" s="4" t="n"/>
+      <c r="W30" s="4" t="n"/>
+      <c r="X30" s="4" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="4" t="n"/>
@@ -2337,7 +2619,7 @@
         </is>
       </c>
       <c r="D31" s="17">
-        <f>SUM(F7:F20)-SUM(H7:H20)-SUM(J7:J20)-SUM(L7:L20)</f>
+        <f>SUM(P7:P20)</f>
         <v/>
       </c>
       <c r="E31" s="18" t="n"/>
@@ -2368,6 +2650,11 @@
       <c r="Q31" s="4" t="n"/>
       <c r="R31" s="4" t="n"/>
       <c r="S31" s="4" t="n"/>
+      <c r="T31" s="4" t="n"/>
+      <c r="U31" s="4" t="n"/>
+      <c r="V31" s="4" t="n"/>
+      <c r="W31" s="4" t="n"/>
+      <c r="X31" s="4" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="4" t="n"/>
@@ -2389,20 +2676,25 @@
       <c r="Q32" s="4" t="n"/>
       <c r="R32" s="4" t="n"/>
       <c r="S32" s="4" t="n"/>
+      <c r="T32" s="4" t="n"/>
+      <c r="U32" s="4" t="n"/>
+      <c r="V32" s="4" t="n"/>
+      <c r="W32" s="4" t="n"/>
+      <c r="X32" s="4" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="4" t="n"/>
       <c r="B33" s="4" t="n"/>
-      <c r="C33" s="24" t="inlineStr">
+      <c r="C33" s="25" t="inlineStr">
         <is>
           <t>Contrôle · somme des cinq effets moins la variation</t>
         </is>
       </c>
-      <c r="D33" s="25">
+      <c r="D33" s="26">
         <f>SUM(D26:D30)-(D31-D25)</f>
         <v/>
       </c>
-      <c r="E33" s="26" t="inlineStr">
+      <c r="E33" s="27" t="inlineStr">
         <is>
           <t>doit valoir 0,00 €</t>
         </is>
@@ -2421,6 +2713,11 @@
       <c r="Q33" s="4" t="n"/>
       <c r="R33" s="4" t="n"/>
       <c r="S33" s="4" t="n"/>
+      <c r="T33" s="4" t="n"/>
+      <c r="U33" s="4" t="n"/>
+      <c r="V33" s="4" t="n"/>
+      <c r="W33" s="4" t="n"/>
+      <c r="X33" s="4" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="4" t="n"/>
@@ -2442,6 +2739,11 @@
       <c r="Q34" s="4" t="n"/>
       <c r="R34" s="4" t="n"/>
       <c r="S34" s="4" t="n"/>
+      <c r="T34" s="4" t="n"/>
+      <c r="U34" s="4" t="n"/>
+      <c r="V34" s="4" t="n"/>
+      <c r="W34" s="4" t="n"/>
+      <c r="X34" s="4" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="4" t="n"/>
@@ -2463,6 +2765,11 @@
       <c r="Q35" s="4" t="n"/>
       <c r="R35" s="4" t="n"/>
       <c r="S35" s="4" t="n"/>
+      <c r="T35" s="4" t="n"/>
+      <c r="U35" s="4" t="n"/>
+      <c r="V35" s="4" t="n"/>
+      <c r="W35" s="4" t="n"/>
+      <c r="X35" s="4" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="4" t="n"/>
@@ -2484,6 +2791,11 @@
       <c r="Q36" s="4" t="n"/>
       <c r="R36" s="4" t="n"/>
       <c r="S36" s="4" t="n"/>
+      <c r="T36" s="4" t="n"/>
+      <c r="U36" s="4" t="n"/>
+      <c r="V36" s="4" t="n"/>
+      <c r="W36" s="4" t="n"/>
+      <c r="X36" s="4" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="4" t="n"/>
@@ -2505,6 +2817,11 @@
       <c r="Q37" s="4" t="n"/>
       <c r="R37" s="4" t="n"/>
       <c r="S37" s="4" t="n"/>
+      <c r="T37" s="4" t="n"/>
+      <c r="U37" s="4" t="n"/>
+      <c r="V37" s="4" t="n"/>
+      <c r="W37" s="4" t="n"/>
+      <c r="X37" s="4" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="4" t="n"/>
@@ -2526,6 +2843,11 @@
       <c r="Q38" s="4" t="n"/>
       <c r="R38" s="4" t="n"/>
       <c r="S38" s="4" t="n"/>
+      <c r="T38" s="4" t="n"/>
+      <c r="U38" s="4" t="n"/>
+      <c r="V38" s="4" t="n"/>
+      <c r="W38" s="4" t="n"/>
+      <c r="X38" s="4" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="4" t="n"/>
@@ -2547,6 +2869,11 @@
       <c r="Q39" s="4" t="n"/>
       <c r="R39" s="4" t="n"/>
       <c r="S39" s="4" t="n"/>
+      <c r="T39" s="4" t="n"/>
+      <c r="U39" s="4" t="n"/>
+      <c r="V39" s="4" t="n"/>
+      <c r="W39" s="4" t="n"/>
+      <c r="X39" s="4" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="4" t="n"/>
@@ -2568,6 +2895,11 @@
       <c r="Q40" s="4" t="n"/>
       <c r="R40" s="4" t="n"/>
       <c r="S40" s="4" t="n"/>
+      <c r="T40" s="4" t="n"/>
+      <c r="U40" s="4" t="n"/>
+      <c r="V40" s="4" t="n"/>
+      <c r="W40" s="4" t="n"/>
+      <c r="X40" s="4" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="4" t="n"/>
@@ -2589,6 +2921,11 @@
       <c r="Q41" s="4" t="n"/>
       <c r="R41" s="4" t="n"/>
       <c r="S41" s="4" t="n"/>
+      <c r="T41" s="4" t="n"/>
+      <c r="U41" s="4" t="n"/>
+      <c r="V41" s="4" t="n"/>
+      <c r="W41" s="4" t="n"/>
+      <c r="X41" s="4" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="4" t="n"/>
@@ -2610,6 +2947,11 @@
       <c r="Q42" s="4" t="n"/>
       <c r="R42" s="4" t="n"/>
       <c r="S42" s="4" t="n"/>
+      <c r="T42" s="4" t="n"/>
+      <c r="U42" s="4" t="n"/>
+      <c r="V42" s="4" t="n"/>
+      <c r="W42" s="4" t="n"/>
+      <c r="X42" s="4" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="4" t="n"/>
@@ -2631,6 +2973,11 @@
       <c r="Q43" s="4" t="n"/>
       <c r="R43" s="4" t="n"/>
       <c r="S43" s="4" t="n"/>
+      <c r="T43" s="4" t="n"/>
+      <c r="U43" s="4" t="n"/>
+      <c r="V43" s="4" t="n"/>
+      <c r="W43" s="4" t="n"/>
+      <c r="X43" s="4" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="4" t="n"/>
@@ -2652,6 +2999,11 @@
       <c r="Q44" s="4" t="n"/>
       <c r="R44" s="4" t="n"/>
       <c r="S44" s="4" t="n"/>
+      <c r="T44" s="4" t="n"/>
+      <c r="U44" s="4" t="n"/>
+      <c r="V44" s="4" t="n"/>
+      <c r="W44" s="4" t="n"/>
+      <c r="X44" s="4" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="4" t="n"/>
@@ -2673,6 +3025,11 @@
       <c r="Q45" s="4" t="n"/>
       <c r="R45" s="4" t="n"/>
       <c r="S45" s="4" t="n"/>
+      <c r="T45" s="4" t="n"/>
+      <c r="U45" s="4" t="n"/>
+      <c r="V45" s="4" t="n"/>
+      <c r="W45" s="4" t="n"/>
+      <c r="X45" s="4" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="4" t="n"/>
@@ -2694,6 +3051,11 @@
       <c r="Q46" s="4" t="n"/>
       <c r="R46" s="4" t="n"/>
       <c r="S46" s="4" t="n"/>
+      <c r="T46" s="4" t="n"/>
+      <c r="U46" s="4" t="n"/>
+      <c r="V46" s="4" t="n"/>
+      <c r="W46" s="4" t="n"/>
+      <c r="X46" s="4" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="4" t="n"/>
@@ -2715,6 +3077,11 @@
       <c r="Q47" s="4" t="n"/>
       <c r="R47" s="4" t="n"/>
       <c r="S47" s="4" t="n"/>
+      <c r="T47" s="4" t="n"/>
+      <c r="U47" s="4" t="n"/>
+      <c r="V47" s="4" t="n"/>
+      <c r="W47" s="4" t="n"/>
+      <c r="X47" s="4" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="4" t="n"/>
@@ -2736,6 +3103,11 @@
       <c r="Q48" s="4" t="n"/>
       <c r="R48" s="4" t="n"/>
       <c r="S48" s="4" t="n"/>
+      <c r="T48" s="4" t="n"/>
+      <c r="U48" s="4" t="n"/>
+      <c r="V48" s="4" t="n"/>
+      <c r="W48" s="4" t="n"/>
+      <c r="X48" s="4" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="4" t="n"/>
@@ -2757,6 +3129,11 @@
       <c r="Q49" s="4" t="n"/>
       <c r="R49" s="4" t="n"/>
       <c r="S49" s="4" t="n"/>
+      <c r="T49" s="4" t="n"/>
+      <c r="U49" s="4" t="n"/>
+      <c r="V49" s="4" t="n"/>
+      <c r="W49" s="4" t="n"/>
+      <c r="X49" s="4" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="4" t="n"/>
@@ -2778,6 +3155,11 @@
       <c r="Q50" s="4" t="n"/>
       <c r="R50" s="4" t="n"/>
       <c r="S50" s="4" t="n"/>
+      <c r="T50" s="4" t="n"/>
+      <c r="U50" s="4" t="n"/>
+      <c r="V50" s="4" t="n"/>
+      <c r="W50" s="4" t="n"/>
+      <c r="X50" s="4" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="4" t="n"/>
@@ -2799,6 +3181,11 @@
       <c r="Q51" s="4" t="n"/>
       <c r="R51" s="4" t="n"/>
       <c r="S51" s="4" t="n"/>
+      <c r="T51" s="4" t="n"/>
+      <c r="U51" s="4" t="n"/>
+      <c r="V51" s="4" t="n"/>
+      <c r="W51" s="4" t="n"/>
+      <c r="X51" s="4" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="4" t="n"/>
@@ -2820,6 +3207,11 @@
       <c r="Q52" s="4" t="n"/>
       <c r="R52" s="4" t="n"/>
       <c r="S52" s="4" t="n"/>
+      <c r="T52" s="4" t="n"/>
+      <c r="U52" s="4" t="n"/>
+      <c r="V52" s="4" t="n"/>
+      <c r="W52" s="4" t="n"/>
+      <c r="X52" s="4" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="4" t="n"/>
@@ -2841,6 +3233,11 @@
       <c r="Q53" s="4" t="n"/>
       <c r="R53" s="4" t="n"/>
       <c r="S53" s="4" t="n"/>
+      <c r="T53" s="4" t="n"/>
+      <c r="U53" s="4" t="n"/>
+      <c r="V53" s="4" t="n"/>
+      <c r="W53" s="4" t="n"/>
+      <c r="X53" s="4" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="4" t="n"/>
@@ -2862,6 +3259,11 @@
       <c r="Q54" s="4" t="n"/>
       <c r="R54" s="4" t="n"/>
       <c r="S54" s="4" t="n"/>
+      <c r="T54" s="4" t="n"/>
+      <c r="U54" s="4" t="n"/>
+      <c r="V54" s="4" t="n"/>
+      <c r="W54" s="4" t="n"/>
+      <c r="X54" s="4" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="4" t="n"/>
@@ -2883,6 +3285,11 @@
       <c r="Q55" s="4" t="n"/>
       <c r="R55" s="4" t="n"/>
       <c r="S55" s="4" t="n"/>
+      <c r="T55" s="4" t="n"/>
+      <c r="U55" s="4" t="n"/>
+      <c r="V55" s="4" t="n"/>
+      <c r="W55" s="4" t="n"/>
+      <c r="X55" s="4" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="4" t="n"/>
@@ -2904,6 +3311,11 @@
       <c r="Q56" s="4" t="n"/>
       <c r="R56" s="4" t="n"/>
       <c r="S56" s="4" t="n"/>
+      <c r="T56" s="4" t="n"/>
+      <c r="U56" s="4" t="n"/>
+      <c r="V56" s="4" t="n"/>
+      <c r="W56" s="4" t="n"/>
+      <c r="X56" s="4" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="4" t="n"/>
@@ -2925,6 +3337,11 @@
       <c r="Q57" s="4" t="n"/>
       <c r="R57" s="4" t="n"/>
       <c r="S57" s="4" t="n"/>
+      <c r="T57" s="4" t="n"/>
+      <c r="U57" s="4" t="n"/>
+      <c r="V57" s="4" t="n"/>
+      <c r="W57" s="4" t="n"/>
+      <c r="X57" s="4" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="4" t="n"/>
@@ -2946,6 +3363,11 @@
       <c r="Q58" s="4" t="n"/>
       <c r="R58" s="4" t="n"/>
       <c r="S58" s="4" t="n"/>
+      <c r="T58" s="4" t="n"/>
+      <c r="U58" s="4" t="n"/>
+      <c r="V58" s="4" t="n"/>
+      <c r="W58" s="4" t="n"/>
+      <c r="X58" s="4" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="4" t="n"/>
@@ -2967,6 +3389,11 @@
       <c r="Q59" s="4" t="n"/>
       <c r="R59" s="4" t="n"/>
       <c r="S59" s="4" t="n"/>
+      <c r="T59" s="4" t="n"/>
+      <c r="U59" s="4" t="n"/>
+      <c r="V59" s="4" t="n"/>
+      <c r="W59" s="4" t="n"/>
+      <c r="X59" s="4" t="n"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="D26:D30">

--- a/eduservices/DRILL1_EXCEL.xlsx
+++ b/eduservices/DRILL1_EXCEL.xlsx
@@ -186,7 +186,7 @@
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="6" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -788,27 +788,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.5" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
-    <col width="11" customWidth="1" min="12" max="12"/>
-    <col width="11" customWidth="1" min="13" max="13"/>
-    <col width="11" customWidth="1" min="14" max="14"/>
-    <col width="11" customWidth="1" min="15" max="15"/>
-    <col width="11" customWidth="1" min="16" max="16"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
     <col width="3" customWidth="1" min="18" max="18"/>
-    <col width="13" customWidth="1" min="19" max="19"/>
-    <col width="13" customWidth="1" min="20" max="20"/>
-    <col width="13" customWidth="1" min="21" max="21"/>
-    <col width="13" customWidth="1" min="22" max="22"/>
-    <col width="13" customWidth="1" min="23" max="23"/>
+    <col width="15" customWidth="1" min="19" max="19"/>
+    <col width="15" customWidth="1" min="20" max="20"/>
+    <col width="15" customWidth="1" min="21" max="21"/>
+    <col width="15" customWidth="1" min="22" max="22"/>
+    <col width="15" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1" ht="8" customHeight="1">
@@ -927,7 +927,7 @@
       <c r="A5" s="4" t="n"/>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>Q_D1_SOCLE — ce que la requête renvoie</t>
+          <t>CE QUE LA REQUÊTE RENVOIE  ·  Q_D1_SOCLE</t>
         </is>
       </c>
       <c r="C5" s="4" t="n"/>
@@ -945,14 +945,14 @@
       <c r="O5" s="4" t="n"/>
       <c r="P5" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">valeurs  </t>
+          <t xml:space="preserve">une ligne par campus  </t>
         </is>
       </c>
       <c r="Q5" s="4" t="n"/>
       <c r="R5" s="4" t="n"/>
       <c r="S5" s="5" t="inlineStr">
         <is>
-          <t>Les cinq effets, calculés ici</t>
+          <t>CE QUE LE CLASSEUR CALCULE</t>
         </is>
       </c>
       <c r="T5" s="4" t="n"/>
@@ -960,113 +960,113 @@
       <c r="V5" s="4" t="n"/>
       <c r="W5" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">une multiplication chacun  </t>
+          <t xml:space="preserve">une multiplication par effet, aucune division  </t>
         </is>
       </c>
       <c r="X5" s="4" t="n"/>
     </row>
-    <row r="6" ht="16" customHeight="1">
+    <row r="6" ht="30" customHeight="1">
       <c r="A6" s="4" t="n"/>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>LIBELLE</t>
+          <t>Campus</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>EFF_P</t>
+          <t>Effectifs 2025</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>EFF_N</t>
+          <t>Effectifs 2026</t>
         </is>
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>D_EFF</t>
+          <t>Élèves gagnés</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>CAE_P</t>
+          <t>CA par élève 2025</t>
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>CAE_N</t>
+          <t>CA par élève 2026</t>
         </is>
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
-          <t>CVE_P</t>
+          <t>Coût var. par élève 2025</t>
         </is>
       </c>
       <c r="I6" s="8" t="inlineStr">
         <is>
-          <t>CVE_N</t>
+          <t>Coût var. par élève 2026</t>
         </is>
       </c>
       <c r="J6" s="8" t="inlineStr">
         <is>
-          <t>MARGE_UNIT_P</t>
+          <t>Marge sur coût var. par élève 2025</t>
         </is>
       </c>
       <c r="K6" s="8" t="inlineStr">
         <is>
-          <t>CDIR_P</t>
+          <t>Coûts directs 2025</t>
         </is>
       </c>
       <c r="L6" s="8" t="inlineStr">
         <is>
-          <t>CDIR_N</t>
+          <t>Coûts directs 2026</t>
         </is>
       </c>
       <c r="M6" s="8" t="inlineStr">
         <is>
-          <t>SIEGE_P</t>
+          <t>Siège 2025</t>
         </is>
       </c>
       <c r="N6" s="8" t="inlineStr">
         <is>
-          <t>SIEGE_N</t>
+          <t>Siège 2026</t>
         </is>
       </c>
       <c r="O6" s="8" t="inlineStr">
         <is>
-          <t>EBITDA_P</t>
+          <t>EBITDA 2025</t>
         </is>
       </c>
       <c r="P6" s="8" t="inlineStr">
         <is>
-          <t>EBITDA_N</t>
+          <t>EBITDA 2026</t>
         </is>
       </c>
       <c r="Q6" s="4" t="n"/>
       <c r="R6" s="4" t="n"/>
       <c r="S6" s="7" t="inlineStr">
         <is>
-          <t>Effectifs</t>
+          <t>Effet effectifs</t>
         </is>
       </c>
       <c r="T6" s="8" t="inlineStr">
         <is>
-          <t>Prix et mix</t>
+          <t>Effet prix et mix</t>
         </is>
       </c>
       <c r="U6" s="8" t="inlineStr">
         <is>
-          <t>Coût var. unit.</t>
+          <t>Effet coût var. unitaire</t>
         </is>
       </c>
       <c r="V6" s="8" t="inlineStr">
         <is>
-          <t>Coûts directs</t>
+          <t>Effet coûts directs</t>
         </is>
       </c>
       <c r="W6" s="8" t="inlineStr">
         <is>
-          <t>Siège</t>
+          <t>Effet siège</t>
         </is>
       </c>
       <c r="X6" s="4" t="n"/>
@@ -2097,7 +2097,7 @@
       <c r="A21" s="4" t="n"/>
       <c r="B21" s="13" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>TOTAL du périmètre</t>
         </is>
       </c>
       <c r="C21" s="14">
@@ -2195,7 +2195,7 @@
       <c r="A23" s="4" t="n"/>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>Le tableau du drill</t>
+          <t>LE TABLEAU DU DRILL</t>
         </is>
       </c>
       <c r="C23" s="4" t="n"/>
@@ -2208,7 +2208,7 @@
       <c r="F23" s="4" t="n"/>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>La cascade du graphe</t>
+          <t>LA CASCADE DU GRAPHE</t>
         </is>
       </c>
       <c r="H23" s="4" t="n"/>
@@ -2233,52 +2233,52 @@
       <c r="W23" s="4" t="n"/>
       <c r="X23" s="4" t="n"/>
     </row>
-    <row r="24">
+    <row r="24" ht="30" customHeight="1">
       <c r="A24" s="4" t="n"/>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>RANG</t>
+          <t>Ordre</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>EFFET</t>
+          <t>Effet</t>
         </is>
       </c>
       <c r="D24" s="8" t="inlineStr">
         <is>
-          <t>MONTANT</t>
+          <t>Montant</t>
         </is>
       </c>
       <c r="E24" s="8" t="inlineStr">
         <is>
-          <t>PART_VAR</t>
+          <t>Part de la variation</t>
         </is>
       </c>
       <c r="F24" s="4" t="n"/>
       <c r="G24" s="7" t="inlineStr">
         <is>
-          <t>ETAPE</t>
+          <t>Étape</t>
         </is>
       </c>
       <c r="H24" s="8" t="inlineStr">
         <is>
-          <t>SOCLE</t>
+          <t>Socle invisible</t>
         </is>
       </c>
       <c r="I24" s="8" t="inlineStr">
         <is>
-          <t>ANCRE</t>
+          <t>Ancre</t>
         </is>
       </c>
       <c r="J24" s="8" t="inlineStr">
         <is>
-          <t>HAUSSE</t>
+          <t>Hausse</t>
         </is>
       </c>
       <c r="K24" s="8" t="inlineStr">
         <is>
-          <t>BAISSE</t>
+          <t>Baisse</t>
         </is>
       </c>
       <c r="L24" s="4" t="n"/>
@@ -2687,7 +2687,7 @@
       <c r="B33" s="4" t="n"/>
       <c r="C33" s="25" t="inlineStr">
         <is>
-          <t>Contrôle · somme des cinq effets moins la variation</t>
+          <t>Contrôle · les cinq effets moins la variation d’EBITDA</t>
         </is>
       </c>
       <c r="D33" s="26">

--- a/eduservices/DRILL1_EXCEL.xlsx
+++ b/eduservices/DRILL1_EXCEL.xlsx
@@ -789,18 +789,18 @@
   <cols>
     <col width="2.5" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
     <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
-    <col width="13" customWidth="1" min="12" max="12"/>
-    <col width="13" customWidth="1" min="13" max="13"/>
-    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="19" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="13" customWidth="1" min="16" max="16"/>
     <col width="3" customWidth="1" min="18" max="18"/>
@@ -965,7 +965,7 @@
       </c>
       <c r="X5" s="4" t="n"/>
     </row>
-    <row r="6" ht="30" customHeight="1">
+    <row r="6" ht="42" customHeight="1">
       <c r="A6" s="4" t="n"/>
       <c r="B6" s="7" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
       <c r="W23" s="4" t="n"/>
       <c r="X23" s="4" t="n"/>
     </row>
-    <row r="24" ht="30" customHeight="1">
+    <row r="24" ht="42" customHeight="1">
       <c r="A24" s="4" t="n"/>
       <c r="B24" s="7" t="inlineStr">
         <is>

--- a/eduservices/DRILL1_EXCEL.xlsx
+++ b/eduservices/DRILL1_EXCEL.xlsx
@@ -16,12 +16,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="#,##0&quot; €&quot;"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
-    <numFmt numFmtId="166" formatCode="0.00&quot; €&quot;"/>
+    <numFmt numFmtId="166" formatCode="+#,##0&quot; €&quot;"/>
+    <numFmt numFmtId="167" formatCode="-#,##0&quot; €&quot;"/>
+    <numFmt numFmtId="168" formatCode="0.00&quot; €&quot;"/>
   </numFmts>
-  <fonts count="15">
+  <fonts count="17">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -96,6 +98,18 @@
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="001E9E89"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00D64545"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="001E9E89"/>
       <sz val="11"/>
     </font>
     <font>
@@ -110,7 +124,7 @@
       <sz val="8.5"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -140,6 +154,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF1E8"/>
       </patternFill>
     </fill>
     <fill>
@@ -195,7 +214,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -239,34 +258,46 @@
     <xf numFmtId="165" fontId="10" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="166" fontId="12" fillId="7" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="12" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="13" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="14" fillId="8" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="3" fontId="13" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="15" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="4" fontId="10" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="13" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="15" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="3" fontId="14" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="16" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="14" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="16" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1542,7 +1573,7 @@
       <c r="C27" s="4" t="n"/>
       <c r="D27" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">la légende du graphe  </t>
+          <t xml:space="preserve">chaque effet rapporté à sa masse : ce qui pousse, ou ce qui freine  </t>
         </is>
       </c>
       <c r="E27" s="4" t="n"/>
@@ -1579,7 +1610,7 @@
       </c>
       <c r="D28" s="10" t="inlineStr">
         <is>
-          <t>Part de la variation</t>
+          <t>Part de sa masse</t>
         </is>
       </c>
       <c r="E28" s="4" t="n"/>
@@ -1664,7 +1695,7 @@
         <v/>
       </c>
       <c r="D30" s="16">
-        <f>IFERROR(C30/(C35-C29),"")</f>
+        <f>IFERROR(IF(C30&gt;0,C30/SUMIF($C$30:$C$34,"&gt;0"),C30/SUMIF($C$30:$C$34,"&lt;0")),"")</f>
         <v/>
       </c>
       <c r="E30" s="4" t="n"/>
@@ -1719,7 +1750,7 @@
         <v/>
       </c>
       <c r="D31" s="16">
-        <f>IFERROR(C31/(C35-C29),"")</f>
+        <f>IFERROR(IF(C31&gt;0,C31/SUMIF($C$30:$C$34,"&gt;0"),C31/SUMIF($C$30:$C$34,"&lt;0")),"")</f>
         <v/>
       </c>
       <c r="E31" s="4" t="n"/>
@@ -1774,7 +1805,7 @@
         <v/>
       </c>
       <c r="D32" s="16">
-        <f>IFERROR(C32/(C35-C29),"")</f>
+        <f>IFERROR(IF(C32&gt;0,C32/SUMIF($C$30:$C$34,"&gt;0"),C32/SUMIF($C$30:$C$34,"&lt;0")),"")</f>
         <v/>
       </c>
       <c r="E32" s="4" t="n"/>
@@ -1829,7 +1860,7 @@
         <v/>
       </c>
       <c r="D33" s="16">
-        <f>IFERROR(C33/(C35-C29),"")</f>
+        <f>IFERROR(IF(C33&gt;0,C33/SUMIF($C$30:$C$34,"&gt;0"),C33/SUMIF($C$30:$C$34,"&lt;0")),"")</f>
         <v/>
       </c>
       <c r="E33" s="4" t="n"/>
@@ -1884,7 +1915,7 @@
         <v/>
       </c>
       <c r="D34" s="16">
-        <f>IFERROR(C34/(C35-C29),"")</f>
+        <f>IFERROR(IF(C34&gt;0,C34/SUMIF($C$30:$C$34,"&gt;0"),C34/SUMIF($C$30:$C$34,"&lt;0")),"")</f>
         <v/>
       </c>
       <c r="E34" s="4" t="n"/>
@@ -1979,9 +2010,19 @@
     </row>
     <row r="36">
       <c r="A36" s="4" t="n"/>
-      <c r="B36" s="4" t="n"/>
-      <c r="C36" s="4" t="n"/>
-      <c r="D36" s="4" t="n"/>
+      <c r="B36" s="17" t="inlineStr">
+        <is>
+          <t>Ce qui pousse  ·  ce qui freine</t>
+        </is>
+      </c>
+      <c r="C36" s="18">
+        <f>SUMIF($C$30:$C$34,"&gt;0")</f>
+        <v/>
+      </c>
+      <c r="D36" s="19">
+        <f>SUMIF($C$30:$C$34,"&lt;0")</f>
+        <v/>
+      </c>
       <c r="E36" s="4" t="n"/>
       <c r="F36" s="4" t="n"/>
       <c r="G36" s="4" t="n"/>
@@ -2004,7 +2045,11 @@
     </row>
     <row r="37">
       <c r="A37" s="4" t="n"/>
-      <c r="B37" s="4" t="n"/>
+      <c r="B37" s="20" t="inlineStr">
+        <is>
+          <t>la variation nette est le SOLDE de ces deux masses, pas un mouvement : c'est pourquoi chaque effet est rapporté à la sienne</t>
+        </is>
+      </c>
       <c r="C37" s="4" t="n"/>
       <c r="D37" s="4" t="n"/>
       <c r="E37" s="4" t="n"/>
@@ -2029,16 +2074,16 @@
     </row>
     <row r="38">
       <c r="A38" s="4" t="n"/>
-      <c r="B38" s="17" t="inlineStr">
+      <c r="B38" s="21" t="inlineStr">
         <is>
           <t>Contrôle · les cinq effets moins la variation</t>
         </is>
       </c>
-      <c r="C38" s="18">
+      <c r="C38" s="22">
         <f>SUM(C30:C34)-(C35-C29)</f>
         <v/>
       </c>
-      <c r="D38" s="19" t="inlineStr">
+      <c r="D38" s="23" t="inlineStr">
         <is>
           <t>doit valoir 0,00 €</t>
         </is>
@@ -2261,1486 +2306,1486 @@
     </row>
     <row r="43">
       <c r="A43" s="4" t="n"/>
-      <c r="B43" s="20" t="inlineStr">
+      <c r="B43" s="24" t="inlineStr">
         <is>
           <t>TOTAL du périmètre</t>
         </is>
       </c>
-      <c r="C43" s="21">
+      <c r="C43" s="25">
         <f>SUM(C44:C73)</f>
         <v/>
       </c>
-      <c r="D43" s="21">
+      <c r="D43" s="25">
         <f>SUM(D44:D73)</f>
         <v/>
       </c>
-      <c r="E43" s="21">
+      <c r="E43" s="25">
         <f>SUM(E44:E73)</f>
         <v/>
       </c>
-      <c r="F43" s="22" t="inlineStr">
+      <c r="F43" s="26" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G43" s="23" t="n"/>
-      <c r="H43" s="23" t="n"/>
-      <c r="I43" s="23" t="n"/>
-      <c r="J43" s="23" t="n"/>
-      <c r="K43" s="21">
+      <c r="G43" s="27" t="n"/>
+      <c r="H43" s="27" t="n"/>
+      <c r="I43" s="27" t="n"/>
+      <c r="J43" s="27" t="n"/>
+      <c r="K43" s="25">
         <f>SUM(K44:K73)</f>
         <v/>
       </c>
-      <c r="L43" s="21">
+      <c r="L43" s="25">
         <f>SUM(L44:L73)</f>
         <v/>
       </c>
-      <c r="M43" s="21">
+      <c r="M43" s="25">
         <f>SUM(M44:M73)</f>
         <v/>
       </c>
-      <c r="N43" s="21">
+      <c r="N43" s="25">
         <f>SUM(N44:N73)</f>
         <v/>
       </c>
-      <c r="O43" s="21">
+      <c r="O43" s="25">
         <f>SUM(O44:O73)</f>
         <v/>
       </c>
-      <c r="P43" s="21">
+      <c r="P43" s="25">
         <f>SUM(P44:P73)</f>
         <v/>
       </c>
       <c r="Q43" s="4" t="n"/>
       <c r="R43" s="4" t="n"/>
-      <c r="S43" s="21">
+      <c r="S43" s="25">
         <f>SUM(S44:S73)</f>
         <v/>
       </c>
-      <c r="T43" s="21">
+      <c r="T43" s="25">
         <f>SUM(T44:T73)</f>
         <v/>
       </c>
-      <c r="U43" s="21">
+      <c r="U43" s="25">
         <f>SUM(U44:U73)</f>
         <v/>
       </c>
-      <c r="V43" s="21">
+      <c r="V43" s="25">
         <f>SUM(V44:V73)</f>
         <v/>
       </c>
-      <c r="W43" s="21">
+      <c r="W43" s="25">
         <f>SUM(W44:W73)</f>
         <v/>
       </c>
     </row>
     <row r="44" ht="15.5" customHeight="1">
       <c r="A44" s="4" t="n"/>
-      <c r="B44" s="24" t="inlineStr">
+      <c r="B44" s="28" t="inlineStr">
         <is>
           <t>ISCOM Lille</t>
         </is>
       </c>
-      <c r="C44" s="25" t="n">
+      <c r="C44" s="29" t="n">
         <v>229</v>
       </c>
-      <c r="D44" s="25" t="n">
+      <c r="D44" s="29" t="n">
         <v>244</v>
       </c>
-      <c r="E44" s="25" t="n">
+      <c r="E44" s="29" t="n">
         <v>15</v>
       </c>
-      <c r="F44" s="26" t="n">
+      <c r="F44" s="30" t="n">
         <v>7196.50655</v>
       </c>
-      <c r="G44" s="26" t="n">
+      <c r="G44" s="30" t="n">
         <v>7196.106557</v>
       </c>
-      <c r="H44" s="26" t="n">
+      <c r="H44" s="30" t="n">
         <v>981.7074239999999</v>
       </c>
-      <c r="I44" s="26" t="n">
+      <c r="I44" s="30" t="n">
         <v>970.245902</v>
       </c>
-      <c r="J44" s="26" t="n">
+      <c r="J44" s="30" t="n">
         <v>6214.799127</v>
       </c>
-      <c r="K44" s="25" t="n">
+      <c r="K44" s="29" t="n">
         <v>901529.53</v>
       </c>
-      <c r="L44" s="25" t="n">
+      <c r="L44" s="29" t="n">
         <v>948506.29</v>
       </c>
-      <c r="M44" s="25" t="n">
+      <c r="M44" s="29" t="n">
         <v>261958.4339533122</v>
       </c>
-      <c r="N44" s="25" t="n">
+      <c r="N44" s="29" t="n">
         <v>280833.8246002989</v>
       </c>
-      <c r="O44" s="25" t="n">
+      <c r="O44" s="29" t="n">
         <v>259701.0360466878</v>
       </c>
-      <c r="P44" s="25" t="n">
+      <c r="P44" s="29" t="n">
         <v>289769.8853997011</v>
       </c>
       <c r="Q44" s="4" t="n"/>
       <c r="R44" s="4" t="n"/>
-      <c r="S44" s="25">
+      <c r="S44" s="29">
         <f>E44*J44</f>
         <v/>
       </c>
-      <c r="T44" s="25">
+      <c r="T44" s="29">
         <f>(G44-F44)*D44</f>
         <v/>
       </c>
-      <c r="U44" s="25">
+      <c r="U44" s="29">
         <f>-(I44-H44)*D44</f>
         <v/>
       </c>
-      <c r="V44" s="25">
+      <c r="V44" s="29">
         <f>-(L44-K44)</f>
         <v/>
       </c>
-      <c r="W44" s="25">
+      <c r="W44" s="29">
         <f>-(N44-M44)</f>
         <v/>
       </c>
     </row>
     <row r="45" ht="15.5" customHeight="1">
       <c r="A45" s="4" t="n"/>
-      <c r="B45" s="24" t="inlineStr">
+      <c r="B45" s="28" t="inlineStr">
         <is>
           <t>ISCOM Paris</t>
         </is>
       </c>
-      <c r="C45" s="25" t="n">
+      <c r="C45" s="29" t="n">
         <v>334</v>
       </c>
-      <c r="D45" s="25" t="n">
+      <c r="D45" s="29" t="n">
         <v>354</v>
       </c>
-      <c r="E45" s="25" t="n">
+      <c r="E45" s="29" t="n">
         <v>20</v>
       </c>
-      <c r="F45" s="26" t="n">
+      <c r="F45" s="30" t="n">
         <v>8217.005988000001</v>
       </c>
-      <c r="G45" s="26" t="n">
+      <c r="G45" s="30" t="n">
         <v>8216.723164000001</v>
       </c>
-      <c r="H45" s="26" t="n">
+      <c r="H45" s="30" t="n">
         <v>1059.389222</v>
       </c>
-      <c r="I45" s="26" t="n">
+      <c r="I45" s="30" t="n">
         <v>1055.412429</v>
       </c>
-      <c r="J45" s="26" t="n">
+      <c r="J45" s="30" t="n">
         <v>7157.616766</v>
       </c>
-      <c r="K45" s="25" t="n">
+      <c r="K45" s="29" t="n">
         <v>1532006.33</v>
       </c>
-      <c r="L45" s="25" t="n">
+      <c r="L45" s="29" t="n">
         <v>1601085.78</v>
       </c>
-      <c r="M45" s="25" t="n">
+      <c r="M45" s="29" t="n">
         <v>382070.6040951031</v>
       </c>
-      <c r="N45" s="25" t="n">
+      <c r="N45" s="29" t="n">
         <v>407439.4766752479</v>
       </c>
-      <c r="O45" s="25" t="n">
+      <c r="O45" s="29" t="n">
         <v>476567.0659048968</v>
       </c>
-      <c r="P45" s="25" t="n">
+      <c r="P45" s="29" t="n">
         <v>526578.7433247521</v>
       </c>
       <c r="Q45" s="4" t="n"/>
       <c r="R45" s="4" t="n"/>
-      <c r="S45" s="25">
+      <c r="S45" s="29">
         <f>E45*J45</f>
         <v/>
       </c>
-      <c r="T45" s="25">
+      <c r="T45" s="29">
         <f>(G45-F45)*D45</f>
         <v/>
       </c>
-      <c r="U45" s="25">
+      <c r="U45" s="29">
         <f>-(I45-H45)*D45</f>
         <v/>
       </c>
-      <c r="V45" s="25">
+      <c r="V45" s="29">
         <f>-(L45-K45)</f>
         <v/>
       </c>
-      <c r="W45" s="25">
+      <c r="W45" s="29">
         <f>-(N45-M45)</f>
         <v/>
       </c>
     </row>
     <row r="46" ht="15.5" customHeight="1">
       <c r="A46" s="4" t="n"/>
-      <c r="B46" s="24" t="inlineStr">
+      <c r="B46" s="28" t="inlineStr">
         <is>
           <t>ISCOM Toulouse</t>
         </is>
       </c>
-      <c r="C46" s="25" t="n">
+      <c r="C46" s="29" t="n">
         <v>216</v>
       </c>
-      <c r="D46" s="25" t="n">
+      <c r="D46" s="29" t="n">
         <v>231</v>
       </c>
-      <c r="E46" s="25" t="n">
+      <c r="E46" s="29" t="n">
         <v>15</v>
       </c>
-      <c r="F46" s="26" t="n">
+      <c r="F46" s="30" t="n">
         <v>7047.777778</v>
       </c>
-      <c r="G46" s="26" t="n">
+      <c r="G46" s="30" t="n">
         <v>7047.532468</v>
       </c>
-      <c r="H46" s="26" t="n">
+      <c r="H46" s="30" t="n">
         <v>1006.217593</v>
       </c>
-      <c r="I46" s="26" t="n">
+      <c r="I46" s="30" t="n">
         <v>990.3290040000001</v>
       </c>
-      <c r="J46" s="26" t="n">
+      <c r="J46" s="30" t="n">
         <v>6041.560185</v>
       </c>
-      <c r="K46" s="25" t="n">
+      <c r="K46" s="29" t="n">
         <v>822578.02</v>
       </c>
-      <c r="L46" s="25" t="n">
+      <c r="L46" s="29" t="n">
         <v>869560.28</v>
       </c>
-      <c r="M46" s="25" t="n">
+      <c r="M46" s="29" t="n">
         <v>247087.0060874675</v>
       </c>
-      <c r="N46" s="25" t="n">
+      <c r="N46" s="29" t="n">
         <v>265870.9093532066</v>
       </c>
-      <c r="O46" s="25" t="n">
+      <c r="O46" s="29" t="n">
         <v>235311.9739125325</v>
       </c>
-      <c r="P46" s="25" t="n">
+      <c r="P46" s="29" t="n">
         <v>263782.8106467934</v>
       </c>
       <c r="Q46" s="4" t="n"/>
       <c r="R46" s="4" t="n"/>
-      <c r="S46" s="25">
+      <c r="S46" s="29">
         <f>E46*J46</f>
         <v/>
       </c>
-      <c r="T46" s="25">
+      <c r="T46" s="29">
         <f>(G46-F46)*D46</f>
         <v/>
       </c>
-      <c r="U46" s="25">
+      <c r="U46" s="29">
         <f>-(I46-H46)*D46</f>
         <v/>
       </c>
-      <c r="V46" s="25">
+      <c r="V46" s="29">
         <f>-(L46-K46)</f>
         <v/>
       </c>
-      <c r="W46" s="25">
+      <c r="W46" s="29">
         <f>-(N46-M46)</f>
         <v/>
       </c>
     </row>
     <row r="47" ht="15.5" customHeight="1">
       <c r="A47" s="4" t="n"/>
-      <c r="B47" s="24" t="inlineStr">
+      <c r="B47" s="28" t="inlineStr">
         <is>
           <t>Ipac Montpellier</t>
         </is>
       </c>
-      <c r="C47" s="25" t="n">
+      <c r="C47" s="29" t="n">
         <v>111</v>
       </c>
-      <c r="D47" s="25" t="n">
+      <c r="D47" s="29" t="n">
         <v>117</v>
       </c>
-      <c r="E47" s="25" t="n">
+      <c r="E47" s="29" t="n">
         <v>6</v>
       </c>
-      <c r="F47" s="26" t="n">
+      <c r="F47" s="30" t="n">
         <v>6680.810811</v>
       </c>
-      <c r="G47" s="26" t="n">
+      <c r="G47" s="30" t="n">
         <v>6680.769231</v>
       </c>
-      <c r="H47" s="26" t="n">
+      <c r="H47" s="30" t="n">
         <v>1121.504505</v>
       </c>
-      <c r="I47" s="26" t="n">
+      <c r="I47" s="30" t="n">
         <v>1120.948718</v>
       </c>
-      <c r="J47" s="26" t="n">
+      <c r="J47" s="30" t="n">
         <v>5559.306306</v>
       </c>
-      <c r="K47" s="25" t="n">
+      <c r="K47" s="29" t="n">
         <v>398826.0100000001</v>
       </c>
-      <c r="L47" s="25" t="n">
+      <c r="L47" s="29" t="n">
         <v>410605.25</v>
       </c>
-      <c r="M47" s="25" t="n">
+      <c r="M47" s="29" t="n">
         <v>124469.3147420315</v>
       </c>
-      <c r="N47" s="25" t="n">
+      <c r="N47" s="29" t="n">
         <v>132004.2356159417</v>
       </c>
-      <c r="O47" s="25" t="n">
+      <c r="O47" s="29" t="n">
         <v>93787.6752579684</v>
       </c>
-      <c r="P47" s="25" t="n">
+      <c r="P47" s="29" t="n">
         <v>107889.5143840583</v>
       </c>
       <c r="Q47" s="4" t="n"/>
       <c r="R47" s="4" t="n"/>
-      <c r="S47" s="25">
+      <c r="S47" s="29">
         <f>E47*J47</f>
         <v/>
       </c>
-      <c r="T47" s="25">
+      <c r="T47" s="29">
         <f>(G47-F47)*D47</f>
         <v/>
       </c>
-      <c r="U47" s="25">
+      <c r="U47" s="29">
         <f>-(I47-H47)*D47</f>
         <v/>
       </c>
-      <c r="V47" s="25">
+      <c r="V47" s="29">
         <f>-(L47-K47)</f>
         <v/>
       </c>
-      <c r="W47" s="25">
+      <c r="W47" s="29">
         <f>-(N47-M47)</f>
         <v/>
       </c>
     </row>
     <row r="48" ht="15.5" customHeight="1">
       <c r="A48" s="4" t="n"/>
-      <c r="B48" s="24" t="inlineStr">
+      <c r="B48" s="28" t="inlineStr">
         <is>
           <t>Ipac Nantes</t>
         </is>
       </c>
-      <c r="C48" s="25" t="n">
+      <c r="C48" s="29" t="n">
         <v>136</v>
       </c>
-      <c r="D48" s="25" t="n">
+      <c r="D48" s="29" t="n">
         <v>145</v>
       </c>
-      <c r="E48" s="25" t="n">
+      <c r="E48" s="29" t="n">
         <v>9</v>
       </c>
-      <c r="F48" s="26" t="n">
+      <c r="F48" s="30" t="n">
         <v>7031.102941</v>
       </c>
-      <c r="G48" s="26" t="n">
+      <c r="G48" s="30" t="n">
         <v>7031.034483</v>
       </c>
-      <c r="H48" s="26" t="n">
+      <c r="H48" s="30" t="n">
         <v>1032.455882</v>
       </c>
-      <c r="I48" s="26" t="n">
+      <c r="I48" s="30" t="n">
         <v>1021.737931</v>
       </c>
-      <c r="J48" s="26" t="n">
+      <c r="J48" s="30" t="n">
         <v>5998.647059</v>
       </c>
-      <c r="K48" s="25" t="n">
+      <c r="K48" s="29" t="n">
         <v>533738.6800000001</v>
       </c>
-      <c r="L48" s="25" t="n">
+      <c r="L48" s="29" t="n">
         <v>557856.2</v>
       </c>
-      <c r="M48" s="25" t="n">
+      <c r="M48" s="29" t="n">
         <v>152502.7022939203</v>
       </c>
-      <c r="N48" s="25" t="n">
+      <c r="N48" s="29" t="n">
         <v>163594.7333690526</v>
       </c>
-      <c r="O48" s="25" t="n">
+      <c r="O48" s="29" t="n">
         <v>129574.6177060797</v>
       </c>
-      <c r="P48" s="25" t="n">
+      <c r="P48" s="29" t="n">
         <v>149897.0666309475</v>
       </c>
       <c r="Q48" s="4" t="n"/>
       <c r="R48" s="4" t="n"/>
-      <c r="S48" s="25">
+      <c r="S48" s="29">
         <f>E48*J48</f>
         <v/>
       </c>
-      <c r="T48" s="25">
+      <c r="T48" s="29">
         <f>(G48-F48)*D48</f>
         <v/>
       </c>
-      <c r="U48" s="25">
+      <c r="U48" s="29">
         <f>-(I48-H48)*D48</f>
         <v/>
       </c>
-      <c r="V48" s="25">
+      <c r="V48" s="29">
         <f>-(L48-K48)</f>
         <v/>
       </c>
-      <c r="W48" s="25">
+      <c r="W48" s="29">
         <f>-(N48-M48)</f>
         <v/>
       </c>
     </row>
     <row r="49" ht="15.5" customHeight="1">
       <c r="A49" s="4" t="n"/>
-      <c r="B49" s="24" t="inlineStr">
+      <c r="B49" s="28" t="inlineStr">
         <is>
           <t>Ipac Rennes</t>
         </is>
       </c>
-      <c r="C49" s="25" t="n">
+      <c r="C49" s="29" t="n">
         <v>111</v>
       </c>
-      <c r="D49" s="25" t="n">
+      <c r="D49" s="29" t="n">
         <v>117</v>
       </c>
-      <c r="E49" s="25" t="n">
+      <c r="E49" s="29" t="n">
         <v>6</v>
       </c>
-      <c r="F49" s="26" t="n">
+      <c r="F49" s="30" t="n">
         <v>6680.810811</v>
       </c>
-      <c r="G49" s="26" t="n">
+      <c r="G49" s="30" t="n">
         <v>6680.769231</v>
       </c>
-      <c r="H49" s="26" t="n">
+      <c r="H49" s="30" t="n">
         <v>1119.495495</v>
       </c>
-      <c r="I49" s="26" t="n">
+      <c r="I49" s="30" t="n">
         <v>1118.854701</v>
       </c>
-      <c r="J49" s="26" t="n">
+      <c r="J49" s="30" t="n">
         <v>5561.315315</v>
       </c>
-      <c r="K49" s="25" t="n">
+      <c r="K49" s="29" t="n">
         <v>399049.03</v>
       </c>
-      <c r="L49" s="25" t="n">
+      <c r="L49" s="29" t="n">
         <v>410850.2499999999</v>
       </c>
-      <c r="M49" s="25" t="n">
+      <c r="M49" s="29" t="n">
         <v>124469.3147420315</v>
       </c>
-      <c r="N49" s="25" t="n">
+      <c r="N49" s="29" t="n">
         <v>132004.2356159417</v>
       </c>
-      <c r="O49" s="25" t="n">
+      <c r="O49" s="29" t="n">
         <v>93787.65525796849</v>
       </c>
-      <c r="P49" s="25" t="n">
+      <c r="P49" s="29" t="n">
         <v>107889.5143840584</v>
       </c>
       <c r="Q49" s="4" t="n"/>
       <c r="R49" s="4" t="n"/>
-      <c r="S49" s="25">
+      <c r="S49" s="29">
         <f>E49*J49</f>
         <v/>
       </c>
-      <c r="T49" s="25">
+      <c r="T49" s="29">
         <f>(G49-F49)*D49</f>
         <v/>
       </c>
-      <c r="U49" s="25">
+      <c r="U49" s="29">
         <f>-(I49-H49)*D49</f>
         <v/>
       </c>
-      <c r="V49" s="25">
+      <c r="V49" s="29">
         <f>-(L49-K49)</f>
         <v/>
       </c>
-      <c r="W49" s="25">
+      <c r="W49" s="29">
         <f>-(N49-M49)</f>
         <v/>
       </c>
     </row>
     <row r="50" ht="15.5" customHeight="1">
       <c r="A50" s="4" t="n"/>
-      <c r="B50" s="24" t="inlineStr">
+      <c r="B50" s="28" t="inlineStr">
         <is>
           <t>MBway Bordeaux</t>
         </is>
       </c>
-      <c r="C50" s="25" t="n">
+      <c r="C50" s="29" t="n">
         <v>234</v>
       </c>
-      <c r="D50" s="25" t="n">
+      <c r="D50" s="29" t="n">
         <v>249</v>
       </c>
-      <c r="E50" s="25" t="n">
+      <c r="E50" s="29" t="n">
         <v>15</v>
       </c>
-      <c r="F50" s="26" t="n">
+      <c r="F50" s="30" t="n">
         <v>7123.311966</v>
       </c>
-      <c r="G50" s="26" t="n">
+      <c r="G50" s="30" t="n">
         <v>7122.931727</v>
       </c>
-      <c r="H50" s="26" t="n">
+      <c r="H50" s="30" t="n">
         <v>967.162393</v>
       </c>
-      <c r="I50" s="26" t="n">
+      <c r="I50" s="30" t="n">
         <v>957.044177</v>
       </c>
-      <c r="J50" s="26" t="n">
+      <c r="J50" s="30" t="n">
         <v>6156.149573</v>
       </c>
-      <c r="K50" s="25" t="n">
+      <c r="K50" s="29" t="n">
         <v>901334.7799999998</v>
       </c>
-      <c r="L50" s="25" t="n">
+      <c r="L50" s="29" t="n">
         <v>943075.91</v>
       </c>
-      <c r="M50" s="25" t="n">
+      <c r="M50" s="29" t="n">
         <v>268151.2278180838</v>
       </c>
-      <c r="N50" s="25" t="n">
+      <c r="N50" s="29" t="n">
         <v>287095.221903666</v>
       </c>
-      <c r="O50" s="25" t="n">
+      <c r="O50" s="29" t="n">
         <v>271052.9921819164</v>
       </c>
-      <c r="P50" s="25" t="n">
+      <c r="P50" s="29" t="n">
         <v>305134.8680963339</v>
       </c>
       <c r="Q50" s="4" t="n"/>
       <c r="R50" s="4" t="n"/>
-      <c r="S50" s="25">
+      <c r="S50" s="29">
         <f>E50*J50</f>
         <v/>
       </c>
-      <c r="T50" s="25">
+      <c r="T50" s="29">
         <f>(G50-F50)*D50</f>
         <v/>
       </c>
-      <c r="U50" s="25">
+      <c r="U50" s="29">
         <f>-(I50-H50)*D50</f>
         <v/>
       </c>
-      <c r="V50" s="25">
+      <c r="V50" s="29">
         <f>-(L50-K50)</f>
         <v/>
       </c>
-      <c r="W50" s="25">
+      <c r="W50" s="29">
         <f>-(N50-M50)</f>
         <v/>
       </c>
     </row>
     <row r="51" ht="15.5" customHeight="1">
       <c r="A51" s="4" t="n"/>
-      <c r="B51" s="24" t="inlineStr">
+      <c r="B51" s="28" t="inlineStr">
         <is>
           <t>MBway Lyon</t>
         </is>
       </c>
-      <c r="C51" s="25" t="n">
+      <c r="C51" s="29" t="n">
         <v>304</v>
       </c>
-      <c r="D51" s="25" t="n">
+      <c r="D51" s="29" t="n">
         <v>324</v>
       </c>
-      <c r="E51" s="25" t="n">
+      <c r="E51" s="29" t="n">
         <v>20</v>
       </c>
-      <c r="F51" s="26" t="n">
+      <c r="F51" s="30" t="n">
         <v>7706.200658</v>
       </c>
-      <c r="G51" s="26" t="n">
+      <c r="G51" s="30" t="n">
         <v>7705.87963</v>
       </c>
-      <c r="H51" s="26" t="n">
+      <c r="H51" s="30" t="n">
         <v>996.2171049999999</v>
       </c>
-      <c r="I51" s="26" t="n">
+      <c r="I51" s="30" t="n">
         <v>985.4629629999999</v>
       </c>
-      <c r="J51" s="26" t="n">
+      <c r="J51" s="30" t="n">
         <v>6709.983553</v>
       </c>
-      <c r="K51" s="25" t="n">
+      <c r="K51" s="29" t="n">
         <v>1284681.03</v>
       </c>
-      <c r="L51" s="25" t="n">
+      <c r="L51" s="29" t="n">
         <v>1346872.36</v>
       </c>
-      <c r="M51" s="25" t="n">
+      <c r="M51" s="29" t="n">
         <v>348367.1950673439</v>
       </c>
-      <c r="N51" s="25" t="n">
+      <c r="N51" s="29" t="n">
         <v>373569.4589820922</v>
       </c>
-      <c r="O51" s="25" t="n">
+      <c r="O51" s="29" t="n">
         <v>406786.7749326563</v>
       </c>
-      <c r="P51" s="25" t="n">
+      <c r="P51" s="29" t="n">
         <v>456973.1810179077</v>
       </c>
       <c r="Q51" s="4" t="n"/>
       <c r="R51" s="4" t="n"/>
-      <c r="S51" s="25">
+      <c r="S51" s="29">
         <f>E51*J51</f>
         <v/>
       </c>
-      <c r="T51" s="25">
+      <c r="T51" s="29">
         <f>(G51-F51)*D51</f>
         <v/>
       </c>
-      <c r="U51" s="25">
+      <c r="U51" s="29">
         <f>-(I51-H51)*D51</f>
         <v/>
       </c>
-      <c r="V51" s="25">
+      <c r="V51" s="29">
         <f>-(L51-K51)</f>
         <v/>
       </c>
-      <c r="W51" s="25">
+      <c r="W51" s="29">
         <f>-(N51-M51)</f>
         <v/>
       </c>
     </row>
     <row r="52" ht="15.5" customHeight="1">
       <c r="A52" s="4" t="n"/>
-      <c r="B52" s="24" t="inlineStr">
+      <c r="B52" s="28" t="inlineStr">
         <is>
           <t>MBway Nantes</t>
         </is>
       </c>
-      <c r="C52" s="25" t="n">
+      <c r="C52" s="29" t="n">
         <v>279</v>
       </c>
-      <c r="D52" s="25" t="n">
+      <c r="D52" s="29" t="n">
         <v>294</v>
       </c>
-      <c r="E52" s="25" t="n">
+      <c r="E52" s="29" t="n">
         <v>15</v>
       </c>
-      <c r="F52" s="26" t="n">
+      <c r="F52" s="30" t="n">
         <v>7341.433692</v>
       </c>
-      <c r="G52" s="26" t="n">
+      <c r="G52" s="30" t="n">
         <v>7341.156463</v>
       </c>
-      <c r="H52" s="26" t="n">
+      <c r="H52" s="30" t="n">
         <v>972.591398</v>
       </c>
-      <c r="I52" s="26" t="n">
+      <c r="I52" s="30" t="n">
         <v>972.122449</v>
       </c>
-      <c r="J52" s="26" t="n">
+      <c r="J52" s="30" t="n">
         <v>6368.842294</v>
       </c>
-      <c r="K52" s="25" t="n">
+      <c r="K52" s="29" t="n">
         <v>1111778.52</v>
       </c>
-      <c r="L52" s="25" t="n">
+      <c r="L52" s="29" t="n">
         <v>1149246.53</v>
       </c>
-      <c r="M52" s="25" t="n">
+      <c r="M52" s="29" t="n">
         <v>319718.4864015467</v>
       </c>
-      <c r="N52" s="25" t="n">
+      <c r="N52" s="29" t="n">
         <v>338979.5981499978</v>
       </c>
-      <c r="O52" s="25" t="n">
+      <c r="O52" s="29" t="n">
         <v>345409.9935984532</v>
       </c>
-      <c r="P52" s="25" t="n">
+      <c r="P52" s="29" t="n">
         <v>384269.8718500021</v>
       </c>
       <c r="Q52" s="4" t="n"/>
       <c r="R52" s="4" t="n"/>
-      <c r="S52" s="25">
+      <c r="S52" s="29">
         <f>E52*J52</f>
         <v/>
       </c>
-      <c r="T52" s="25">
+      <c r="T52" s="29">
         <f>(G52-F52)*D52</f>
         <v/>
       </c>
-      <c r="U52" s="25">
+      <c r="U52" s="29">
         <f>-(I52-H52)*D52</f>
         <v/>
       </c>
-      <c r="V52" s="25">
+      <c r="V52" s="29">
         <f>-(L52-K52)</f>
         <v/>
       </c>
-      <c r="W52" s="25">
+      <c r="W52" s="29">
         <f>-(N52-M52)</f>
         <v/>
       </c>
     </row>
     <row r="53" ht="15.5" customHeight="1">
       <c r="A53" s="4" t="n"/>
-      <c r="B53" s="24" t="inlineStr">
+      <c r="B53" s="28" t="inlineStr">
         <is>
           <t>MBway Paris</t>
         </is>
       </c>
-      <c r="C53" s="25" t="n">
+      <c r="C53" s="29" t="n">
         <v>362</v>
       </c>
-      <c r="D53" s="25" t="n">
+      <c r="D53" s="29" t="n">
         <v>382</v>
       </c>
-      <c r="E53" s="25" t="n">
+      <c r="E53" s="29" t="n">
         <v>20</v>
       </c>
-      <c r="F53" s="26" t="n">
+      <c r="F53" s="30" t="n">
         <v>8217.127071999999</v>
       </c>
-      <c r="G53" s="26" t="n">
+      <c r="G53" s="30" t="n">
         <v>8216.858639</v>
       </c>
-      <c r="H53" s="26" t="n">
+      <c r="H53" s="30" t="n">
         <v>1023.732044</v>
       </c>
-      <c r="I53" s="26" t="n">
+      <c r="I53" s="30" t="n">
         <v>1024.934555</v>
       </c>
-      <c r="J53" s="26" t="n">
+      <c r="J53" s="30" t="n">
         <v>7193.395028</v>
       </c>
-      <c r="K53" s="25" t="n">
+      <c r="K53" s="29" t="n">
         <v>1648776.64</v>
       </c>
-      <c r="L53" s="25" t="n">
+      <c r="L53" s="29" t="n">
         <v>1707251.49</v>
       </c>
-      <c r="M53" s="25" t="n">
+      <c r="M53" s="29" t="n">
         <v>414832.3340357959</v>
       </c>
-      <c r="N53" s="25" t="n">
+      <c r="N53" s="29" t="n">
         <v>440443.3705915956</v>
       </c>
-      <c r="O53" s="25" t="n">
+      <c r="O53" s="29" t="n">
         <v>540400.0259642038</v>
       </c>
-      <c r="P53" s="25" t="n">
+      <c r="P53" s="29" t="n">
         <v>599620.1394084045</v>
       </c>
       <c r="Q53" s="4" t="n"/>
       <c r="R53" s="4" t="n"/>
-      <c r="S53" s="25">
+      <c r="S53" s="29">
         <f>E53*J53</f>
         <v/>
       </c>
-      <c r="T53" s="25">
+      <c r="T53" s="29">
         <f>(G53-F53)*D53</f>
         <v/>
       </c>
-      <c r="U53" s="25">
+      <c r="U53" s="29">
         <f>-(I53-H53)*D53</f>
         <v/>
       </c>
-      <c r="V53" s="25">
+      <c r="V53" s="29">
         <f>-(L53-K53)</f>
         <v/>
       </c>
-      <c r="W53" s="25">
+      <c r="W53" s="29">
         <f>-(N53-M53)</f>
         <v/>
       </c>
     </row>
     <row r="54" ht="15.5" customHeight="1">
       <c r="A54" s="4" t="n"/>
-      <c r="B54" s="24" t="inlineStr">
+      <c r="B54" s="28" t="inlineStr">
         <is>
           <t>Pigier Bordeaux</t>
         </is>
       </c>
-      <c r="C54" s="25" t="n">
+      <c r="C54" s="29" t="n">
         <v>166</v>
       </c>
-      <c r="D54" s="25" t="n">
+      <c r="D54" s="29" t="n">
         <v>176</v>
       </c>
-      <c r="E54" s="25" t="n">
+      <c r="E54" s="29" t="n">
         <v>10</v>
       </c>
-      <c r="F54" s="26" t="n">
+      <c r="F54" s="30" t="n">
         <v>6435.361446</v>
       </c>
-      <c r="G54" s="26" t="n">
+      <c r="G54" s="30" t="n">
         <v>6435.511364</v>
       </c>
-      <c r="H54" s="26" t="n">
+      <c r="H54" s="30" t="n">
         <v>979.421687</v>
       </c>
-      <c r="I54" s="26" t="n">
+      <c r="I54" s="30" t="n">
         <v>973.801136</v>
       </c>
-      <c r="J54" s="26" t="n">
+      <c r="J54" s="30" t="n">
         <v>5455.939759</v>
       </c>
-      <c r="K54" s="25" t="n">
+      <c r="K54" s="29" t="n">
         <v>508701.5699999999</v>
       </c>
-      <c r="L54" s="25" t="n">
+      <c r="L54" s="29" t="n">
         <v>530872.76</v>
       </c>
-      <c r="M54" s="25" t="n">
+      <c r="M54" s="29" t="n">
         <v>185745.8159994536</v>
       </c>
-      <c r="N54" s="25" t="n">
+      <c r="N54" s="29" t="n">
         <v>198146.4540348334</v>
       </c>
-      <c r="O54" s="25" t="n">
+      <c r="O54" s="29" t="n">
         <v>211238.6140005465</v>
       </c>
-      <c r="P54" s="25" t="n">
+      <c r="P54" s="29" t="n">
         <v>232241.7859651666</v>
       </c>
       <c r="Q54" s="4" t="n"/>
       <c r="R54" s="4" t="n"/>
-      <c r="S54" s="25">
+      <c r="S54" s="29">
         <f>E54*J54</f>
         <v/>
       </c>
-      <c r="T54" s="25">
+      <c r="T54" s="29">
         <f>(G54-F54)*D54</f>
         <v/>
       </c>
-      <c r="U54" s="25">
+      <c r="U54" s="29">
         <f>-(I54-H54)*D54</f>
         <v/>
       </c>
-      <c r="V54" s="25">
+      <c r="V54" s="29">
         <f>-(L54-K54)</f>
         <v/>
       </c>
-      <c r="W54" s="25">
+      <c r="W54" s="29">
         <f>-(N54-M54)</f>
         <v/>
       </c>
     </row>
     <row r="55" ht="15.5" customHeight="1">
       <c r="A55" s="4" t="n"/>
-      <c r="B55" s="24" t="inlineStr">
+      <c r="B55" s="28" t="inlineStr">
         <is>
           <t>Pigier Lyon</t>
         </is>
       </c>
-      <c r="C55" s="25" t="n">
+      <c r="C55" s="29" t="n">
         <v>211</v>
       </c>
-      <c r="D55" s="25" t="n">
+      <c r="D55" s="29" t="n">
         <v>226</v>
       </c>
-      <c r="E55" s="25" t="n">
+      <c r="E55" s="29" t="n">
         <v>15</v>
       </c>
-      <c r="F55" s="26" t="n">
+      <c r="F55" s="30" t="n">
         <v>6963.696682</v>
       </c>
-      <c r="G55" s="26" t="n">
+      <c r="G55" s="30" t="n">
         <v>6963.849558</v>
       </c>
-      <c r="H55" s="26" t="n">
+      <c r="H55" s="30" t="n">
         <v>900.962085</v>
       </c>
-      <c r="I55" s="26" t="n">
+      <c r="I55" s="30" t="n">
         <v>889.013274</v>
       </c>
-      <c r="J55" s="26" t="n">
+      <c r="J55" s="30" t="n">
         <v>6062.734597</v>
       </c>
-      <c r="K55" s="25" t="n">
+      <c r="K55" s="29" t="n">
         <v>736369.5600000001</v>
       </c>
-      <c r="L55" s="25" t="n">
+      <c r="L55" s="29" t="n">
         <v>778456.91</v>
       </c>
-      <c r="M55" s="25" t="n">
+      <c r="M55" s="29" t="n">
         <v>236099.0885076113</v>
       </c>
-      <c r="N55" s="25" t="n">
+      <c r="N55" s="29" t="n">
         <v>254438.5895015823</v>
       </c>
-      <c r="O55" s="25" t="n">
+      <c r="O55" s="29" t="n">
         <v>306768.3514923886</v>
       </c>
-      <c r="P55" s="25" t="n">
+      <c r="P55" s="29" t="n">
         <v>340017.5004984176</v>
       </c>
       <c r="Q55" s="4" t="n"/>
       <c r="R55" s="4" t="n"/>
-      <c r="S55" s="25">
+      <c r="S55" s="29">
         <f>E55*J55</f>
         <v/>
       </c>
-      <c r="T55" s="25">
+      <c r="T55" s="29">
         <f>(G55-F55)*D55</f>
         <v/>
       </c>
-      <c r="U55" s="25">
+      <c r="U55" s="29">
         <f>-(I55-H55)*D55</f>
         <v/>
       </c>
-      <c r="V55" s="25">
+      <c r="V55" s="29">
         <f>-(L55-K55)</f>
         <v/>
       </c>
-      <c r="W55" s="25">
+      <c r="W55" s="29">
         <f>-(N55-M55)</f>
         <v/>
       </c>
     </row>
     <row r="56" ht="15.5" customHeight="1">
       <c r="A56" s="4" t="n"/>
-      <c r="B56" s="24" t="inlineStr">
+      <c r="B56" s="28" t="inlineStr">
         <is>
           <t>Tunon Lyon</t>
         </is>
       </c>
-      <c r="C56" s="25" t="n">
+      <c r="C56" s="29" t="n">
         <v>111</v>
       </c>
-      <c r="D56" s="25" t="n">
+      <c r="D56" s="29" t="n">
         <v>117</v>
       </c>
-      <c r="E56" s="25" t="n">
+      <c r="E56" s="29" t="n">
         <v>6</v>
       </c>
-      <c r="F56" s="26" t="n">
+      <c r="F56" s="30" t="n">
         <v>7380.810811</v>
       </c>
-      <c r="G56" s="26" t="n">
+      <c r="G56" s="30" t="n">
         <v>7380.769231</v>
       </c>
-      <c r="H56" s="26" t="n">
+      <c r="H56" s="30" t="n">
         <v>1151.576577</v>
       </c>
-      <c r="I56" s="26" t="n">
+      <c r="I56" s="30" t="n">
         <v>1152.333333</v>
       </c>
-      <c r="J56" s="26" t="n">
+      <c r="J56" s="30" t="n">
         <v>6229.234234</v>
       </c>
-      <c r="K56" s="25" t="n">
+      <c r="K56" s="29" t="n">
         <v>523989.18</v>
       </c>
-      <c r="L56" s="25" t="n">
+      <c r="L56" s="29" t="n">
         <v>561046.28</v>
       </c>
-      <c r="M56" s="25" t="n">
+      <c r="M56" s="29" t="n">
         <v>127153.9396992599</v>
       </c>
-      <c r="N56" s="25" t="n">
+      <c r="N56" s="29" t="n">
         <v>134851.3780311536</v>
       </c>
-      <c r="O56" s="25" t="n">
+      <c r="O56" s="29" t="n">
         <v>40301.88030074014</v>
       </c>
-      <c r="P56" s="25" t="n">
+      <c r="P56" s="29" t="n">
         <v>32829.34196884636</v>
       </c>
       <c r="Q56" s="4" t="n"/>
       <c r="R56" s="4" t="n"/>
-      <c r="S56" s="25">
+      <c r="S56" s="29">
         <f>E56*J56</f>
         <v/>
       </c>
-      <c r="T56" s="25">
+      <c r="T56" s="29">
         <f>(G56-F56)*D56</f>
         <v/>
       </c>
-      <c r="U56" s="25">
+      <c r="U56" s="29">
         <f>-(I56-H56)*D56</f>
         <v/>
       </c>
-      <c r="V56" s="25">
+      <c r="V56" s="29">
         <f>-(L56-K56)</f>
         <v/>
       </c>
-      <c r="W56" s="25">
+      <c r="W56" s="29">
         <f>-(N56-M56)</f>
         <v/>
       </c>
     </row>
     <row r="57" ht="15.5" customHeight="1">
       <c r="A57" s="4" t="n"/>
-      <c r="B57" s="24" t="inlineStr">
+      <c r="B57" s="28" t="inlineStr">
         <is>
           <t>Tunon Paris</t>
         </is>
       </c>
-      <c r="C57" s="25" t="n">
+      <c r="C57" s="29" t="n">
         <v>129</v>
       </c>
-      <c r="D57" s="25" t="n">
+      <c r="D57" s="29" t="n">
         <v>138</v>
       </c>
-      <c r="E57" s="25" t="n">
+      <c r="E57" s="29" t="n">
         <v>9</v>
       </c>
-      <c r="F57" s="26" t="n">
+      <c r="F57" s="30" t="n">
         <v>7870.697674</v>
       </c>
-      <c r="G57" s="26" t="n">
+      <c r="G57" s="30" t="n">
         <v>7870.652174</v>
       </c>
-      <c r="H57" s="26" t="n">
+      <c r="H57" s="30" t="n">
         <v>1128.976744</v>
       </c>
-      <c r="I57" s="26" t="n">
+      <c r="I57" s="30" t="n">
         <v>1116.137681</v>
       </c>
-      <c r="J57" s="26" t="n">
+      <c r="J57" s="30" t="n">
         <v>6741.72093</v>
       </c>
-      <c r="K57" s="25" t="n">
+      <c r="K57" s="29" t="n">
         <v>664829.1599999999</v>
       </c>
-      <c r="L57" s="25" t="n">
+      <c r="L57" s="29" t="n">
         <v>724171.6999999998</v>
       </c>
-      <c r="M57" s="25" t="n">
+      <c r="M57" s="29" t="n">
         <v>147773.5365570392</v>
       </c>
-      <c r="N57" s="25" t="n">
+      <c r="N57" s="29" t="n">
         <v>159055.5135753902</v>
       </c>
-      <c r="O57" s="25" t="n">
+      <c r="O57" s="29" t="n">
         <v>57079.30344296087</v>
       </c>
-      <c r="P57" s="25" t="n">
+      <c r="P57" s="29" t="n">
         <v>48895.78642460998</v>
       </c>
       <c r="Q57" s="4" t="n"/>
       <c r="R57" s="4" t="n"/>
-      <c r="S57" s="25">
+      <c r="S57" s="29">
         <f>E57*J57</f>
         <v/>
       </c>
-      <c r="T57" s="25">
+      <c r="T57" s="29">
         <f>(G57-F57)*D57</f>
         <v/>
       </c>
-      <c r="U57" s="25">
+      <c r="U57" s="29">
         <f>-(I57-H57)*D57</f>
         <v/>
       </c>
-      <c r="V57" s="25">
+      <c r="V57" s="29">
         <f>-(L57-K57)</f>
         <v/>
       </c>
-      <c r="W57" s="25">
+      <c r="W57" s="29">
         <f>-(N57-M57)</f>
         <v/>
       </c>
     </row>
     <row r="58" ht="15.5" customHeight="1">
       <c r="A58" s="4" t="n"/>
-      <c r="B58" s="24" t="n"/>
-      <c r="C58" s="25" t="n"/>
-      <c r="D58" s="25" t="n"/>
-      <c r="E58" s="25" t="n"/>
-      <c r="F58" s="26" t="n"/>
-      <c r="G58" s="26" t="n"/>
-      <c r="H58" s="26" t="n"/>
-      <c r="I58" s="26" t="n"/>
-      <c r="J58" s="26" t="n"/>
-      <c r="K58" s="25" t="n"/>
-      <c r="L58" s="25" t="n"/>
-      <c r="M58" s="25" t="n"/>
-      <c r="N58" s="25" t="n"/>
-      <c r="O58" s="25" t="n"/>
-      <c r="P58" s="25" t="n"/>
+      <c r="B58" s="28" t="n"/>
+      <c r="C58" s="29" t="n"/>
+      <c r="D58" s="29" t="n"/>
+      <c r="E58" s="29" t="n"/>
+      <c r="F58" s="30" t="n"/>
+      <c r="G58" s="30" t="n"/>
+      <c r="H58" s="30" t="n"/>
+      <c r="I58" s="30" t="n"/>
+      <c r="J58" s="30" t="n"/>
+      <c r="K58" s="29" t="n"/>
+      <c r="L58" s="29" t="n"/>
+      <c r="M58" s="29" t="n"/>
+      <c r="N58" s="29" t="n"/>
+      <c r="O58" s="29" t="n"/>
+      <c r="P58" s="29" t="n"/>
       <c r="Q58" s="4" t="n"/>
       <c r="R58" s="4" t="n"/>
-      <c r="S58" s="25" t="n"/>
-      <c r="T58" s="25" t="n"/>
-      <c r="U58" s="25" t="n"/>
-      <c r="V58" s="25" t="n"/>
-      <c r="W58" s="25" t="n"/>
+      <c r="S58" s="29" t="n"/>
+      <c r="T58" s="29" t="n"/>
+      <c r="U58" s="29" t="n"/>
+      <c r="V58" s="29" t="n"/>
+      <c r="W58" s="29" t="n"/>
     </row>
     <row r="59" ht="15.5" customHeight="1">
       <c r="A59" s="4" t="n"/>
-      <c r="B59" s="24" t="n"/>
-      <c r="C59" s="25" t="n"/>
-      <c r="D59" s="25" t="n"/>
-      <c r="E59" s="25" t="n"/>
-      <c r="F59" s="26" t="n"/>
-      <c r="G59" s="26" t="n"/>
-      <c r="H59" s="26" t="n"/>
-      <c r="I59" s="26" t="n"/>
-      <c r="J59" s="26" t="n"/>
-      <c r="K59" s="25" t="n"/>
-      <c r="L59" s="25" t="n"/>
-      <c r="M59" s="25" t="n"/>
-      <c r="N59" s="25" t="n"/>
-      <c r="O59" s="25" t="n"/>
-      <c r="P59" s="25" t="n"/>
+      <c r="B59" s="28" t="n"/>
+      <c r="C59" s="29" t="n"/>
+      <c r="D59" s="29" t="n"/>
+      <c r="E59" s="29" t="n"/>
+      <c r="F59" s="30" t="n"/>
+      <c r="G59" s="30" t="n"/>
+      <c r="H59" s="30" t="n"/>
+      <c r="I59" s="30" t="n"/>
+      <c r="J59" s="30" t="n"/>
+      <c r="K59" s="29" t="n"/>
+      <c r="L59" s="29" t="n"/>
+      <c r="M59" s="29" t="n"/>
+      <c r="N59" s="29" t="n"/>
+      <c r="O59" s="29" t="n"/>
+      <c r="P59" s="29" t="n"/>
       <c r="Q59" s="4" t="n"/>
       <c r="R59" s="4" t="n"/>
-      <c r="S59" s="25" t="n"/>
-      <c r="T59" s="25" t="n"/>
-      <c r="U59" s="25" t="n"/>
-      <c r="V59" s="25" t="n"/>
-      <c r="W59" s="25" t="n"/>
+      <c r="S59" s="29" t="n"/>
+      <c r="T59" s="29" t="n"/>
+      <c r="U59" s="29" t="n"/>
+      <c r="V59" s="29" t="n"/>
+      <c r="W59" s="29" t="n"/>
     </row>
     <row r="60" ht="15.5" customHeight="1">
       <c r="A60" s="4" t="n"/>
-      <c r="B60" s="24" t="n"/>
-      <c r="C60" s="25" t="n"/>
-      <c r="D60" s="25" t="n"/>
-      <c r="E60" s="25" t="n"/>
-      <c r="F60" s="26" t="n"/>
-      <c r="G60" s="26" t="n"/>
-      <c r="H60" s="26" t="n"/>
-      <c r="I60" s="26" t="n"/>
-      <c r="J60" s="26" t="n"/>
-      <c r="K60" s="25" t="n"/>
-      <c r="L60" s="25" t="n"/>
-      <c r="M60" s="25" t="n"/>
-      <c r="N60" s="25" t="n"/>
-      <c r="O60" s="25" t="n"/>
-      <c r="P60" s="25" t="n"/>
+      <c r="B60" s="28" t="n"/>
+      <c r="C60" s="29" t="n"/>
+      <c r="D60" s="29" t="n"/>
+      <c r="E60" s="29" t="n"/>
+      <c r="F60" s="30" t="n"/>
+      <c r="G60" s="30" t="n"/>
+      <c r="H60" s="30" t="n"/>
+      <c r="I60" s="30" t="n"/>
+      <c r="J60" s="30" t="n"/>
+      <c r="K60" s="29" t="n"/>
+      <c r="L60" s="29" t="n"/>
+      <c r="M60" s="29" t="n"/>
+      <c r="N60" s="29" t="n"/>
+      <c r="O60" s="29" t="n"/>
+      <c r="P60" s="29" t="n"/>
       <c r="Q60" s="4" t="n"/>
       <c r="R60" s="4" t="n"/>
-      <c r="S60" s="25" t="n"/>
-      <c r="T60" s="25" t="n"/>
-      <c r="U60" s="25" t="n"/>
-      <c r="V60" s="25" t="n"/>
-      <c r="W60" s="25" t="n"/>
+      <c r="S60" s="29" t="n"/>
+      <c r="T60" s="29" t="n"/>
+      <c r="U60" s="29" t="n"/>
+      <c r="V60" s="29" t="n"/>
+      <c r="W60" s="29" t="n"/>
     </row>
     <row r="61" ht="15.5" customHeight="1">
       <c r="A61" s="4" t="n"/>
-      <c r="B61" s="24" t="n"/>
-      <c r="C61" s="25" t="n"/>
-      <c r="D61" s="25" t="n"/>
-      <c r="E61" s="25" t="n"/>
-      <c r="F61" s="26" t="n"/>
-      <c r="G61" s="26" t="n"/>
-      <c r="H61" s="26" t="n"/>
-      <c r="I61" s="26" t="n"/>
-      <c r="J61" s="26" t="n"/>
-      <c r="K61" s="25" t="n"/>
-      <c r="L61" s="25" t="n"/>
-      <c r="M61" s="25" t="n"/>
-      <c r="N61" s="25" t="n"/>
-      <c r="O61" s="25" t="n"/>
-      <c r="P61" s="25" t="n"/>
+      <c r="B61" s="28" t="n"/>
+      <c r="C61" s="29" t="n"/>
+      <c r="D61" s="29" t="n"/>
+      <c r="E61" s="29" t="n"/>
+      <c r="F61" s="30" t="n"/>
+      <c r="G61" s="30" t="n"/>
+      <c r="H61" s="30" t="n"/>
+      <c r="I61" s="30" t="n"/>
+      <c r="J61" s="30" t="n"/>
+      <c r="K61" s="29" t="n"/>
+      <c r="L61" s="29" t="n"/>
+      <c r="M61" s="29" t="n"/>
+      <c r="N61" s="29" t="n"/>
+      <c r="O61" s="29" t="n"/>
+      <c r="P61" s="29" t="n"/>
       <c r="Q61" s="4" t="n"/>
       <c r="R61" s="4" t="n"/>
-      <c r="S61" s="25" t="n"/>
-      <c r="T61" s="25" t="n"/>
-      <c r="U61" s="25" t="n"/>
-      <c r="V61" s="25" t="n"/>
-      <c r="W61" s="25" t="n"/>
+      <c r="S61" s="29" t="n"/>
+      <c r="T61" s="29" t="n"/>
+      <c r="U61" s="29" t="n"/>
+      <c r="V61" s="29" t="n"/>
+      <c r="W61" s="29" t="n"/>
     </row>
     <row r="62" ht="15.5" customHeight="1">
       <c r="A62" s="4" t="n"/>
-      <c r="B62" s="24" t="n"/>
-      <c r="C62" s="25" t="n"/>
-      <c r="D62" s="25" t="n"/>
-      <c r="E62" s="25" t="n"/>
-      <c r="F62" s="26" t="n"/>
-      <c r="G62" s="26" t="n"/>
-      <c r="H62" s="26" t="n"/>
-      <c r="I62" s="26" t="n"/>
-      <c r="J62" s="26" t="n"/>
-      <c r="K62" s="25" t="n"/>
-      <c r="L62" s="25" t="n"/>
-      <c r="M62" s="25" t="n"/>
-      <c r="N62" s="25" t="n"/>
-      <c r="O62" s="25" t="n"/>
-      <c r="P62" s="25" t="n"/>
+      <c r="B62" s="28" t="n"/>
+      <c r="C62" s="29" t="n"/>
+      <c r="D62" s="29" t="n"/>
+      <c r="E62" s="29" t="n"/>
+      <c r="F62" s="30" t="n"/>
+      <c r="G62" s="30" t="n"/>
+      <c r="H62" s="30" t="n"/>
+      <c r="I62" s="30" t="n"/>
+      <c r="J62" s="30" t="n"/>
+      <c r="K62" s="29" t="n"/>
+      <c r="L62" s="29" t="n"/>
+      <c r="M62" s="29" t="n"/>
+      <c r="N62" s="29" t="n"/>
+      <c r="O62" s="29" t="n"/>
+      <c r="P62" s="29" t="n"/>
       <c r="Q62" s="4" t="n"/>
       <c r="R62" s="4" t="n"/>
-      <c r="S62" s="25" t="n"/>
-      <c r="T62" s="25" t="n"/>
-      <c r="U62" s="25" t="n"/>
-      <c r="V62" s="25" t="n"/>
-      <c r="W62" s="25" t="n"/>
+      <c r="S62" s="29" t="n"/>
+      <c r="T62" s="29" t="n"/>
+      <c r="U62" s="29" t="n"/>
+      <c r="V62" s="29" t="n"/>
+      <c r="W62" s="29" t="n"/>
     </row>
     <row r="63" ht="15.5" customHeight="1">
       <c r="A63" s="4" t="n"/>
-      <c r="B63" s="24" t="n"/>
-      <c r="C63" s="25" t="n"/>
-      <c r="D63" s="25" t="n"/>
-      <c r="E63" s="25" t="n"/>
-      <c r="F63" s="26" t="n"/>
-      <c r="G63" s="26" t="n"/>
-      <c r="H63" s="26" t="n"/>
-      <c r="I63" s="26" t="n"/>
-      <c r="J63" s="26" t="n"/>
-      <c r="K63" s="25" t="n"/>
-      <c r="L63" s="25" t="n"/>
-      <c r="M63" s="25" t="n"/>
-      <c r="N63" s="25" t="n"/>
-      <c r="O63" s="25" t="n"/>
-      <c r="P63" s="25" t="n"/>
+      <c r="B63" s="28" t="n"/>
+      <c r="C63" s="29" t="n"/>
+      <c r="D63" s="29" t="n"/>
+      <c r="E63" s="29" t="n"/>
+      <c r="F63" s="30" t="n"/>
+      <c r="G63" s="30" t="n"/>
+      <c r="H63" s="30" t="n"/>
+      <c r="I63" s="30" t="n"/>
+      <c r="J63" s="30" t="n"/>
+      <c r="K63" s="29" t="n"/>
+      <c r="L63" s="29" t="n"/>
+      <c r="M63" s="29" t="n"/>
+      <c r="N63" s="29" t="n"/>
+      <c r="O63" s="29" t="n"/>
+      <c r="P63" s="29" t="n"/>
       <c r="Q63" s="4" t="n"/>
       <c r="R63" s="4" t="n"/>
-      <c r="S63" s="25" t="n"/>
-      <c r="T63" s="25" t="n"/>
-      <c r="U63" s="25" t="n"/>
-      <c r="V63" s="25" t="n"/>
-      <c r="W63" s="25" t="n"/>
+      <c r="S63" s="29" t="n"/>
+      <c r="T63" s="29" t="n"/>
+      <c r="U63" s="29" t="n"/>
+      <c r="V63" s="29" t="n"/>
+      <c r="W63" s="29" t="n"/>
     </row>
     <row r="64" ht="15.5" customHeight="1">
       <c r="A64" s="4" t="n"/>
-      <c r="B64" s="24" t="n"/>
-      <c r="C64" s="25" t="n"/>
-      <c r="D64" s="25" t="n"/>
-      <c r="E64" s="25" t="n"/>
-      <c r="F64" s="26" t="n"/>
-      <c r="G64" s="26" t="n"/>
-      <c r="H64" s="26" t="n"/>
-      <c r="I64" s="26" t="n"/>
-      <c r="J64" s="26" t="n"/>
-      <c r="K64" s="25" t="n"/>
-      <c r="L64" s="25" t="n"/>
-      <c r="M64" s="25" t="n"/>
-      <c r="N64" s="25" t="n"/>
-      <c r="O64" s="25" t="n"/>
-      <c r="P64" s="25" t="n"/>
+      <c r="B64" s="28" t="n"/>
+      <c r="C64" s="29" t="n"/>
+      <c r="D64" s="29" t="n"/>
+      <c r="E64" s="29" t="n"/>
+      <c r="F64" s="30" t="n"/>
+      <c r="G64" s="30" t="n"/>
+      <c r="H64" s="30" t="n"/>
+      <c r="I64" s="30" t="n"/>
+      <c r="J64" s="30" t="n"/>
+      <c r="K64" s="29" t="n"/>
+      <c r="L64" s="29" t="n"/>
+      <c r="M64" s="29" t="n"/>
+      <c r="N64" s="29" t="n"/>
+      <c r="O64" s="29" t="n"/>
+      <c r="P64" s="29" t="n"/>
       <c r="Q64" s="4" t="n"/>
       <c r="R64" s="4" t="n"/>
-      <c r="S64" s="25" t="n"/>
-      <c r="T64" s="25" t="n"/>
-      <c r="U64" s="25" t="n"/>
-      <c r="V64" s="25" t="n"/>
-      <c r="W64" s="25" t="n"/>
+      <c r="S64" s="29" t="n"/>
+      <c r="T64" s="29" t="n"/>
+      <c r="U64" s="29" t="n"/>
+      <c r="V64" s="29" t="n"/>
+      <c r="W64" s="29" t="n"/>
     </row>
     <row r="65" ht="15.5" customHeight="1">
       <c r="A65" s="4" t="n"/>
-      <c r="B65" s="24" t="n"/>
-      <c r="C65" s="25" t="n"/>
-      <c r="D65" s="25" t="n"/>
-      <c r="E65" s="25" t="n"/>
-      <c r="F65" s="26" t="n"/>
-      <c r="G65" s="26" t="n"/>
-      <c r="H65" s="26" t="n"/>
-      <c r="I65" s="26" t="n"/>
-      <c r="J65" s="26" t="n"/>
-      <c r="K65" s="25" t="n"/>
-      <c r="L65" s="25" t="n"/>
-      <c r="M65" s="25" t="n"/>
-      <c r="N65" s="25" t="n"/>
-      <c r="O65" s="25" t="n"/>
-      <c r="P65" s="25" t="n"/>
+      <c r="B65" s="28" t="n"/>
+      <c r="C65" s="29" t="n"/>
+      <c r="D65" s="29" t="n"/>
+      <c r="E65" s="29" t="n"/>
+      <c r="F65" s="30" t="n"/>
+      <c r="G65" s="30" t="n"/>
+      <c r="H65" s="30" t="n"/>
+      <c r="I65" s="30" t="n"/>
+      <c r="J65" s="30" t="n"/>
+      <c r="K65" s="29" t="n"/>
+      <c r="L65" s="29" t="n"/>
+      <c r="M65" s="29" t="n"/>
+      <c r="N65" s="29" t="n"/>
+      <c r="O65" s="29" t="n"/>
+      <c r="P65" s="29" t="n"/>
       <c r="Q65" s="4" t="n"/>
       <c r="R65" s="4" t="n"/>
-      <c r="S65" s="25" t="n"/>
-      <c r="T65" s="25" t="n"/>
-      <c r="U65" s="25" t="n"/>
-      <c r="V65" s="25" t="n"/>
-      <c r="W65" s="25" t="n"/>
+      <c r="S65" s="29" t="n"/>
+      <c r="T65" s="29" t="n"/>
+      <c r="U65" s="29" t="n"/>
+      <c r="V65" s="29" t="n"/>
+      <c r="W65" s="29" t="n"/>
     </row>
     <row r="66" ht="15.5" customHeight="1">
       <c r="A66" s="4" t="n"/>
-      <c r="B66" s="24" t="n"/>
-      <c r="C66" s="25" t="n"/>
-      <c r="D66" s="25" t="n"/>
-      <c r="E66" s="25" t="n"/>
-      <c r="F66" s="26" t="n"/>
-      <c r="G66" s="26" t="n"/>
-      <c r="H66" s="26" t="n"/>
-      <c r="I66" s="26" t="n"/>
-      <c r="J66" s="26" t="n"/>
-      <c r="K66" s="25" t="n"/>
-      <c r="L66" s="25" t="n"/>
-      <c r="M66" s="25" t="n"/>
-      <c r="N66" s="25" t="n"/>
-      <c r="O66" s="25" t="n"/>
-      <c r="P66" s="25" t="n"/>
+      <c r="B66" s="28" t="n"/>
+      <c r="C66" s="29" t="n"/>
+      <c r="D66" s="29" t="n"/>
+      <c r="E66" s="29" t="n"/>
+      <c r="F66" s="30" t="n"/>
+      <c r="G66" s="30" t="n"/>
+      <c r="H66" s="30" t="n"/>
+      <c r="I66" s="30" t="n"/>
+      <c r="J66" s="30" t="n"/>
+      <c r="K66" s="29" t="n"/>
+      <c r="L66" s="29" t="n"/>
+      <c r="M66" s="29" t="n"/>
+      <c r="N66" s="29" t="n"/>
+      <c r="O66" s="29" t="n"/>
+      <c r="P66" s="29" t="n"/>
       <c r="Q66" s="4" t="n"/>
       <c r="R66" s="4" t="n"/>
-      <c r="S66" s="25" t="n"/>
-      <c r="T66" s="25" t="n"/>
-      <c r="U66" s="25" t="n"/>
-      <c r="V66" s="25" t="n"/>
-      <c r="W66" s="25" t="n"/>
+      <c r="S66" s="29" t="n"/>
+      <c r="T66" s="29" t="n"/>
+      <c r="U66" s="29" t="n"/>
+      <c r="V66" s="29" t="n"/>
+      <c r="W66" s="29" t="n"/>
     </row>
     <row r="67" ht="15.5" customHeight="1">
       <c r="A67" s="4" t="n"/>
-      <c r="B67" s="24" t="n"/>
-      <c r="C67" s="25" t="n"/>
-      <c r="D67" s="25" t="n"/>
-      <c r="E67" s="25" t="n"/>
-      <c r="F67" s="26" t="n"/>
-      <c r="G67" s="26" t="n"/>
-      <c r="H67" s="26" t="n"/>
-      <c r="I67" s="26" t="n"/>
-      <c r="J67" s="26" t="n"/>
-      <c r="K67" s="25" t="n"/>
-      <c r="L67" s="25" t="n"/>
-      <c r="M67" s="25" t="n"/>
-      <c r="N67" s="25" t="n"/>
-      <c r="O67" s="25" t="n"/>
-      <c r="P67" s="25" t="n"/>
+      <c r="B67" s="28" t="n"/>
+      <c r="C67" s="29" t="n"/>
+      <c r="D67" s="29" t="n"/>
+      <c r="E67" s="29" t="n"/>
+      <c r="F67" s="30" t="n"/>
+      <c r="G67" s="30" t="n"/>
+      <c r="H67" s="30" t="n"/>
+      <c r="I67" s="30" t="n"/>
+      <c r="J67" s="30" t="n"/>
+      <c r="K67" s="29" t="n"/>
+      <c r="L67" s="29" t="n"/>
+      <c r="M67" s="29" t="n"/>
+      <c r="N67" s="29" t="n"/>
+      <c r="O67" s="29" t="n"/>
+      <c r="P67" s="29" t="n"/>
       <c r="Q67" s="4" t="n"/>
       <c r="R67" s="4" t="n"/>
-      <c r="S67" s="25" t="n"/>
-      <c r="T67" s="25" t="n"/>
-      <c r="U67" s="25" t="n"/>
-      <c r="V67" s="25" t="n"/>
-      <c r="W67" s="25" t="n"/>
+      <c r="S67" s="29" t="n"/>
+      <c r="T67" s="29" t="n"/>
+      <c r="U67" s="29" t="n"/>
+      <c r="V67" s="29" t="n"/>
+      <c r="W67" s="29" t="n"/>
     </row>
     <row r="68" ht="15.5" customHeight="1">
       <c r="A68" s="4" t="n"/>
-      <c r="B68" s="24" t="n"/>
-      <c r="C68" s="25" t="n"/>
-      <c r="D68" s="25" t="n"/>
-      <c r="E68" s="25" t="n"/>
-      <c r="F68" s="26" t="n"/>
-      <c r="G68" s="26" t="n"/>
-      <c r="H68" s="26" t="n"/>
-      <c r="I68" s="26" t="n"/>
-      <c r="J68" s="26" t="n"/>
-      <c r="K68" s="25" t="n"/>
-      <c r="L68" s="25" t="n"/>
-      <c r="M68" s="25" t="n"/>
-      <c r="N68" s="25" t="n"/>
-      <c r="O68" s="25" t="n"/>
-      <c r="P68" s="25" t="n"/>
+      <c r="B68" s="28" t="n"/>
+      <c r="C68" s="29" t="n"/>
+      <c r="D68" s="29" t="n"/>
+      <c r="E68" s="29" t="n"/>
+      <c r="F68" s="30" t="n"/>
+      <c r="G68" s="30" t="n"/>
+      <c r="H68" s="30" t="n"/>
+      <c r="I68" s="30" t="n"/>
+      <c r="J68" s="30" t="n"/>
+      <c r="K68" s="29" t="n"/>
+      <c r="L68" s="29" t="n"/>
+      <c r="M68" s="29" t="n"/>
+      <c r="N68" s="29" t="n"/>
+      <c r="O68" s="29" t="n"/>
+      <c r="P68" s="29" t="n"/>
       <c r="Q68" s="4" t="n"/>
       <c r="R68" s="4" t="n"/>
-      <c r="S68" s="25" t="n"/>
-      <c r="T68" s="25" t="n"/>
-      <c r="U68" s="25" t="n"/>
-      <c r="V68" s="25" t="n"/>
-      <c r="W68" s="25" t="n"/>
+      <c r="S68" s="29" t="n"/>
+      <c r="T68" s="29" t="n"/>
+      <c r="U68" s="29" t="n"/>
+      <c r="V68" s="29" t="n"/>
+      <c r="W68" s="29" t="n"/>
     </row>
     <row r="69" ht="15.5" customHeight="1">
       <c r="A69" s="4" t="n"/>
-      <c r="B69" s="24" t="n"/>
-      <c r="C69" s="25" t="n"/>
-      <c r="D69" s="25" t="n"/>
-      <c r="E69" s="25" t="n"/>
-      <c r="F69" s="26" t="n"/>
-      <c r="G69" s="26" t="n"/>
-      <c r="H69" s="26" t="n"/>
-      <c r="I69" s="26" t="n"/>
-      <c r="J69" s="26" t="n"/>
-      <c r="K69" s="25" t="n"/>
-      <c r="L69" s="25" t="n"/>
-      <c r="M69" s="25" t="n"/>
-      <c r="N69" s="25" t="n"/>
-      <c r="O69" s="25" t="n"/>
-      <c r="P69" s="25" t="n"/>
+      <c r="B69" s="28" t="n"/>
+      <c r="C69" s="29" t="n"/>
+      <c r="D69" s="29" t="n"/>
+      <c r="E69" s="29" t="n"/>
+      <c r="F69" s="30" t="n"/>
+      <c r="G69" s="30" t="n"/>
+      <c r="H69" s="30" t="n"/>
+      <c r="I69" s="30" t="n"/>
+      <c r="J69" s="30" t="n"/>
+      <c r="K69" s="29" t="n"/>
+      <c r="L69" s="29" t="n"/>
+      <c r="M69" s="29" t="n"/>
+      <c r="N69" s="29" t="n"/>
+      <c r="O69" s="29" t="n"/>
+      <c r="P69" s="29" t="n"/>
       <c r="Q69" s="4" t="n"/>
       <c r="R69" s="4" t="n"/>
-      <c r="S69" s="25" t="n"/>
-      <c r="T69" s="25" t="n"/>
-      <c r="U69" s="25" t="n"/>
-      <c r="V69" s="25" t="n"/>
-      <c r="W69" s="25" t="n"/>
+      <c r="S69" s="29" t="n"/>
+      <c r="T69" s="29" t="n"/>
+      <c r="U69" s="29" t="n"/>
+      <c r="V69" s="29" t="n"/>
+      <c r="W69" s="29" t="n"/>
     </row>
     <row r="70" ht="15.5" customHeight="1">
       <c r="A70" s="4" t="n"/>
-      <c r="B70" s="24" t="n"/>
-      <c r="C70" s="25" t="n"/>
-      <c r="D70" s="25" t="n"/>
-      <c r="E70" s="25" t="n"/>
-      <c r="F70" s="26" t="n"/>
-      <c r="G70" s="26" t="n"/>
-      <c r="H70" s="26" t="n"/>
-      <c r="I70" s="26" t="n"/>
-      <c r="J70" s="26" t="n"/>
-      <c r="K70" s="25" t="n"/>
-      <c r="L70" s="25" t="n"/>
-      <c r="M70" s="25" t="n"/>
-      <c r="N70" s="25" t="n"/>
-      <c r="O70" s="25" t="n"/>
-      <c r="P70" s="25" t="n"/>
+      <c r="B70" s="28" t="n"/>
+      <c r="C70" s="29" t="n"/>
+      <c r="D70" s="29" t="n"/>
+      <c r="E70" s="29" t="n"/>
+      <c r="F70" s="30" t="n"/>
+      <c r="G70" s="30" t="n"/>
+      <c r="H70" s="30" t="n"/>
+      <c r="I70" s="30" t="n"/>
+      <c r="J70" s="30" t="n"/>
+      <c r="K70" s="29" t="n"/>
+      <c r="L70" s="29" t="n"/>
+      <c r="M70" s="29" t="n"/>
+      <c r="N70" s="29" t="n"/>
+      <c r="O70" s="29" t="n"/>
+      <c r="P70" s="29" t="n"/>
       <c r="Q70" s="4" t="n"/>
       <c r="R70" s="4" t="n"/>
-      <c r="S70" s="25" t="n"/>
-      <c r="T70" s="25" t="n"/>
-      <c r="U70" s="25" t="n"/>
-      <c r="V70" s="25" t="n"/>
-      <c r="W70" s="25" t="n"/>
+      <c r="S70" s="29" t="n"/>
+      <c r="T70" s="29" t="n"/>
+      <c r="U70" s="29" t="n"/>
+      <c r="V70" s="29" t="n"/>
+      <c r="W70" s="29" t="n"/>
     </row>
     <row r="71" ht="15.5" customHeight="1">
       <c r="A71" s="4" t="n"/>
-      <c r="B71" s="24" t="n"/>
-      <c r="C71" s="25" t="n"/>
-      <c r="D71" s="25" t="n"/>
-      <c r="E71" s="25" t="n"/>
-      <c r="F71" s="26" t="n"/>
-      <c r="G71" s="26" t="n"/>
-      <c r="H71" s="26" t="n"/>
-      <c r="I71" s="26" t="n"/>
-      <c r="J71" s="26" t="n"/>
-      <c r="K71" s="25" t="n"/>
-      <c r="L71" s="25" t="n"/>
-      <c r="M71" s="25" t="n"/>
-      <c r="N71" s="25" t="n"/>
-      <c r="O71" s="25" t="n"/>
-      <c r="P71" s="25" t="n"/>
+      <c r="B71" s="28" t="n"/>
+      <c r="C71" s="29" t="n"/>
+      <c r="D71" s="29" t="n"/>
+      <c r="E71" s="29" t="n"/>
+      <c r="F71" s="30" t="n"/>
+      <c r="G71" s="30" t="n"/>
+      <c r="H71" s="30" t="n"/>
+      <c r="I71" s="30" t="n"/>
+      <c r="J71" s="30" t="n"/>
+      <c r="K71" s="29" t="n"/>
+      <c r="L71" s="29" t="n"/>
+      <c r="M71" s="29" t="n"/>
+      <c r="N71" s="29" t="n"/>
+      <c r="O71" s="29" t="n"/>
+      <c r="P71" s="29" t="n"/>
       <c r="Q71" s="4" t="n"/>
       <c r="R71" s="4" t="n"/>
-      <c r="S71" s="25" t="n"/>
-      <c r="T71" s="25" t="n"/>
-      <c r="U71" s="25" t="n"/>
-      <c r="V71" s="25" t="n"/>
-      <c r="W71" s="25" t="n"/>
+      <c r="S71" s="29" t="n"/>
+      <c r="T71" s="29" t="n"/>
+      <c r="U71" s="29" t="n"/>
+      <c r="V71" s="29" t="n"/>
+      <c r="W71" s="29" t="n"/>
     </row>
     <row r="72" ht="15.5" customHeight="1">
       <c r="A72" s="4" t="n"/>
-      <c r="B72" s="24" t="n"/>
-      <c r="C72" s="25" t="n"/>
-      <c r="D72" s="25" t="n"/>
-      <c r="E72" s="25" t="n"/>
-      <c r="F72" s="26" t="n"/>
-      <c r="G72" s="26" t="n"/>
-      <c r="H72" s="26" t="n"/>
-      <c r="I72" s="26" t="n"/>
-      <c r="J72" s="26" t="n"/>
-      <c r="K72" s="25" t="n"/>
-      <c r="L72" s="25" t="n"/>
-      <c r="M72" s="25" t="n"/>
-      <c r="N72" s="25" t="n"/>
-      <c r="O72" s="25" t="n"/>
-      <c r="P72" s="25" t="n"/>
+      <c r="B72" s="28" t="n"/>
+      <c r="C72" s="29" t="n"/>
+      <c r="D72" s="29" t="n"/>
+      <c r="E72" s="29" t="n"/>
+      <c r="F72" s="30" t="n"/>
+      <c r="G72" s="30" t="n"/>
+      <c r="H72" s="30" t="n"/>
+      <c r="I72" s="30" t="n"/>
+      <c r="J72" s="30" t="n"/>
+      <c r="K72" s="29" t="n"/>
+      <c r="L72" s="29" t="n"/>
+      <c r="M72" s="29" t="n"/>
+      <c r="N72" s="29" t="n"/>
+      <c r="O72" s="29" t="n"/>
+      <c r="P72" s="29" t="n"/>
       <c r="Q72" s="4" t="n"/>
       <c r="R72" s="4" t="n"/>
-      <c r="S72" s="25" t="n"/>
-      <c r="T72" s="25" t="n"/>
-      <c r="U72" s="25" t="n"/>
-      <c r="V72" s="25" t="n"/>
-      <c r="W72" s="25" t="n"/>
+      <c r="S72" s="29" t="n"/>
+      <c r="T72" s="29" t="n"/>
+      <c r="U72" s="29" t="n"/>
+      <c r="V72" s="29" t="n"/>
+      <c r="W72" s="29" t="n"/>
     </row>
     <row r="73" ht="15.5" customHeight="1">
       <c r="A73" s="4" t="n"/>
-      <c r="B73" s="24" t="n"/>
-      <c r="C73" s="25" t="n"/>
-      <c r="D73" s="25" t="n"/>
-      <c r="E73" s="25" t="n"/>
-      <c r="F73" s="26" t="n"/>
-      <c r="G73" s="26" t="n"/>
-      <c r="H73" s="26" t="n"/>
-      <c r="I73" s="26" t="n"/>
-      <c r="J73" s="26" t="n"/>
-      <c r="K73" s="25" t="n"/>
-      <c r="L73" s="25" t="n"/>
-      <c r="M73" s="25" t="n"/>
-      <c r="N73" s="25" t="n"/>
-      <c r="O73" s="25" t="n"/>
-      <c r="P73" s="25" t="n"/>
+      <c r="B73" s="28" t="n"/>
+      <c r="C73" s="29" t="n"/>
+      <c r="D73" s="29" t="n"/>
+      <c r="E73" s="29" t="n"/>
+      <c r="F73" s="30" t="n"/>
+      <c r="G73" s="30" t="n"/>
+      <c r="H73" s="30" t="n"/>
+      <c r="I73" s="30" t="n"/>
+      <c r="J73" s="30" t="n"/>
+      <c r="K73" s="29" t="n"/>
+      <c r="L73" s="29" t="n"/>
+      <c r="M73" s="29" t="n"/>
+      <c r="N73" s="29" t="n"/>
+      <c r="O73" s="29" t="n"/>
+      <c r="P73" s="29" t="n"/>
       <c r="Q73" s="4" t="n"/>
       <c r="R73" s="4" t="n"/>
-      <c r="S73" s="25" t="n"/>
-      <c r="T73" s="25" t="n"/>
-      <c r="U73" s="25" t="n"/>
-      <c r="V73" s="25" t="n"/>
-      <c r="W73" s="25" t="n"/>
+      <c r="S73" s="29" t="n"/>
+      <c r="T73" s="29" t="n"/>
+      <c r="U73" s="29" t="n"/>
+      <c r="V73" s="29" t="n"/>
+      <c r="W73" s="29" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="4" t="n"/>
